--- a/script/templates/WePartyInterface_BS.xlsx
+++ b/script/templates/WePartyInterface_BS.xlsx
@@ -456,7 +456,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>53265</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -483,7 +483,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>53228</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -510,7 +510,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>BSTA4600</t>
+          <t>30691</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -537,7 +537,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>BSTA4600</t>
+          <t>30691</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -564,7 +564,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BSTA4600</t>
+          <t>30691</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -591,7 +591,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BSTA4600</t>
+          <t>30691</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BSTA5000</t>
+          <t>30691</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -645,7 +645,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BSTA5000</t>
+          <t>30691</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -672,7 +672,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>35164</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>35164</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>35164</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>35164</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>35164</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>35164</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BSU4500</t>
+          <t>71123</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>71123</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>BAA9909</t>
+          <t>71123</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>71123</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>DIP007</t>
+          <t>71123</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>71123</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>71123</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>BSU1405</t>
+          <t>72136</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1050,7 +1050,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>BSU4500</t>
+          <t>72136</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>72136</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>BAA9909</t>
+          <t>72136</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>72136</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>72136</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>BAA9909</t>
+          <t>72136</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>72136</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>BSU1405</t>
+          <t>70466</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>70466</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>BSU4500</t>
+          <t>70466</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>70466</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>BAA9909</t>
+          <t>70466</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>70466</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>70466</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>BSU4500</t>
+          <t>31360</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>31360</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>BSOP3310</t>
+          <t>31360</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>BAA9909</t>
+          <t>31360</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>31360</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>BSU1405</t>
+          <t>76475</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>76475</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>BSU4500</t>
+          <t>76475</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1644,7 +1644,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>76475</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>76475</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>BSOP3310</t>
+          <t>76475</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>76475</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>BAA9909</t>
+          <t>30313</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>30313</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>BSU4500</t>
+          <t>30313</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>30313</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1860,7 +1860,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>30313</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>BAA9909</t>
+          <t>30313</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>30313</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>30313</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1968,7 +1968,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>30313</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1995,7 +1995,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>BAA9909</t>
+          <t>35775</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>35775</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2049,7 +2049,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>BSU4500</t>
+          <t>35775</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>35775</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2103,7 +2103,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>35775</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>35775</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2157,7 +2157,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>35775</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>35775</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>BAA9909</t>
+          <t>78555</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>BSU4500</t>
+          <t>78555</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>78555</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>78555</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>BSOP3310</t>
+          <t>78555</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2346,7 +2346,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>78555</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2373,7 +2373,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>78555</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2400,7 +2400,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>78555</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2427,7 +2427,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>71208</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>BSU4500</t>
+          <t>71208</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>71208</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>71208</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2535,7 +2535,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>BAA9909</t>
+          <t>71208</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>71208</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>71208</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>BAA9909</t>
+          <t>38378</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>BSU1405</t>
+          <t>38378</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>38378</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>38378</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2724,7 +2724,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>38378</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -2751,7 +2751,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>BAA9909</t>
+          <t>38378</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -2778,7 +2778,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>38378</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -2805,7 +2805,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>38378</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -2832,7 +2832,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>BAA9909</t>
+          <t>72172</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -2859,7 +2859,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>BSU1405</t>
+          <t>72172</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>72172</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -2913,7 +2913,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>BSU4500</t>
+          <t>72172</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>72172</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -2967,7 +2967,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>72172</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>72172</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>BAA9909</t>
+          <t>79123</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>BSU4500</t>
+          <t>79123</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>79123</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>BAA9909</t>
+          <t>79123</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3129,7 +3129,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>79123</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>BAA9909</t>
+          <t>79123</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -3183,7 +3183,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>79123</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>79123</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>BSEA14081</t>
+          <t>78474</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>DIP007</t>
+          <t>70656</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -3291,7 +3291,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>DIP007</t>
+          <t>70656</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>BSU4500</t>
+          <t>70656</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -3345,7 +3345,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>70656</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -3372,7 +3372,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>BAA9909</t>
+          <t>70656</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -3399,7 +3399,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>BAA9909</t>
+          <t>70656</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>70656</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>BSU4500</t>
+          <t>76351</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>BAA9909</t>
+          <t>76351</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -3507,7 +3507,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>76351</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>BSOP1911</t>
+          <t>76351</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -3561,7 +3561,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>BSOP1911</t>
+          <t>76351</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -3588,7 +3588,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>76351</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -3615,7 +3615,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>37670</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -3642,7 +3642,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>37670</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -3669,7 +3669,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>37670</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>BAA9909</t>
+          <t>37670</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -3723,7 +3723,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>37670</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>DIP007</t>
+          <t>37670</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -3777,7 +3777,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>BAA9909</t>
+          <t>37670</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>BSU4500</t>
+          <t>33144</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -3831,7 +3831,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>33144</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>BAA9909</t>
+          <t>33144</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>33144</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>33144</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -3939,7 +3939,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>33144</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>BSTA4800-1</t>
+          <t>76338</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>BSTA4800-1</t>
+          <t>76338</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -4020,7 +4020,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>BSTA4800-1</t>
+          <t>76338</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -4047,7 +4047,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>BSTA4800-1</t>
+          <t>76338</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>BSTA4800-1</t>
+          <t>76338</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>BSTA4800-1</t>
+          <t>76338</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>BSTA4800-1</t>
+          <t>76338</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>BSU4500</t>
+          <t>70499</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>70499</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>BAA9909</t>
+          <t>70499</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>70499</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -4263,7 +4263,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>70499</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>70499</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -4317,7 +4317,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>BSTA4810</t>
+          <t>78706</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -4344,7 +4344,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>BSTA4810</t>
+          <t>78706</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>78706</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>BSTA4810</t>
+          <t>78706</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -4425,7 +4425,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>78706</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -4452,7 +4452,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>BSEA14081</t>
+          <t>76025</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -4479,7 +4479,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>76025</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>76164</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -4533,7 +4533,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>76164</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>BSU1409-7</t>
+          <t>79509</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -4587,7 +4587,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>BSU1409-7</t>
+          <t>79509</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -4614,7 +4614,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>BSU4500</t>
+          <t>32349</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>32349</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>32349</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>32349</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -4722,7 +4722,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>32349</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -4749,7 +4749,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>32349</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -4776,7 +4776,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>31216</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -4803,7 +4803,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>BSU4500</t>
+          <t>31216</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>31216</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>BAA9909</t>
+          <t>31216</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -4884,7 +4884,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>31216</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -4911,7 +4911,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>BSU4500</t>
+          <t>71653</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>71653</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -4965,7 +4965,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>71653</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -4992,7 +4992,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>71653</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>71653</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>71653</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -5073,7 +5073,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>BSU4500</t>
+          <t>71679</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -5100,7 +5100,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>71679</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -5127,7 +5127,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>71679</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -5154,7 +5154,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>BSMP1300</t>
+          <t>71679</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -5181,7 +5181,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>BAA9909</t>
+          <t>71679</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -5208,7 +5208,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>71679</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -5235,7 +5235,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>71679</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -5262,7 +5262,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>BSU4500</t>
+          <t>38426</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -5289,7 +5289,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>38426</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>38426</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>38426</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -5370,7 +5370,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>38426</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -5397,7 +5397,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>BAA9909</t>
+          <t>38426</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -5424,7 +5424,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>38426</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -5451,7 +5451,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>38426</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -5476,11 +5476,6 @@
           <t>S16</t>
         </is>
       </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>BSTA1002</t>
-        </is>
-      </c>
       <c r="D188" t="inlineStr">
         <is>
           <t>01/01/2026</t>
@@ -5503,11 +5498,6 @@
           <t>S15</t>
         </is>
       </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>BSTA4111</t>
-        </is>
-      </c>
       <c r="D189" t="inlineStr">
         <is>
           <t>01/01/2026</t>
@@ -5530,11 +5520,6 @@
           <t>S14</t>
         </is>
       </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>BSTA4111</t>
-        </is>
-      </c>
       <c r="D190" t="inlineStr">
         <is>
           <t>01/01/2026</t>
@@ -5557,11 +5542,6 @@
           <t>S13</t>
         </is>
       </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>BSTA4111</t>
-        </is>
-      </c>
       <c r="D191" t="inlineStr">
         <is>
           <t>01/01/2026</t>
@@ -5584,11 +5564,6 @@
           <t>S12</t>
         </is>
       </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>BSTA4111</t>
-        </is>
-      </c>
       <c r="D192" t="inlineStr">
         <is>
           <t>01/01/2026</t>
@@ -5611,11 +5586,6 @@
           <t>E01</t>
         </is>
       </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>DIP010</t>
-        </is>
-      </c>
       <c r="D193" t="inlineStr">
         <is>
           <t>01/01/2026</t>
@@ -5640,7 +5610,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>BSU4500</t>
+          <t>79354</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -5667,7 +5637,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>79354</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -5694,7 +5664,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>79354</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -5721,7 +5691,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>79354</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -5748,7 +5718,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>79354</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -5775,7 +5745,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>79354</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -5802,7 +5772,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>79354</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -5829,7 +5799,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>79354</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -5856,7 +5826,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>79354</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -5883,7 +5853,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>78392</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -5910,7 +5880,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>78392</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -5937,7 +5907,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>BAA9909</t>
+          <t>78392</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -5964,7 +5934,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>78392</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -5991,7 +5961,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>78392</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -6018,7 +5988,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>78392</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -6045,7 +6015,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>34295</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -6072,7 +6042,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>BAA9909</t>
+          <t>34295</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -6099,7 +6069,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>34295</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -6126,7 +6096,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>34295</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -6153,7 +6123,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>BAA9909</t>
+          <t>34295</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -6180,7 +6150,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>DIP007</t>
+          <t>34295</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -6207,7 +6177,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>BSU4500</t>
+          <t>30235</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -6234,7 +6204,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>30235</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -6261,7 +6231,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>BAA9909</t>
+          <t>30235</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -6288,7 +6258,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>30235</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -6315,7 +6285,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>BAA9909</t>
+          <t>30235</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -6342,7 +6312,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>30235</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -6369,7 +6339,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>30235</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -6396,7 +6366,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>BSTA4100</t>
+          <t>35946</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -6423,7 +6393,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>35946</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -6450,7 +6420,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>35946</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -6477,7 +6447,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>35946</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -6504,7 +6474,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>BSEA2600</t>
+          <t>35946</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -6531,7 +6501,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>BSTA4100</t>
+          <t>35946</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -6558,7 +6528,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>32815</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -6585,7 +6555,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>32815</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -6612,7 +6582,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>32815</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -6639,7 +6609,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>BAA9909</t>
+          <t>32815</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -6666,7 +6636,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>BAA9909</t>
+          <t>32815</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -6693,7 +6663,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>32815</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -6720,7 +6690,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>33479</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -6747,7 +6717,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>33479</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -6774,7 +6744,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>33479</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -6801,7 +6771,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>BSCS0510</t>
+          <t>33479</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -6828,7 +6798,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>33479</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -6855,7 +6825,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>36999</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -6882,7 +6852,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>BSU4500</t>
+          <t>36999</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -6909,7 +6879,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>36999</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -6936,7 +6906,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>BAA9909</t>
+          <t>36999</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -6963,7 +6933,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>BSOP3310</t>
+          <t>36999</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -6990,7 +6960,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>BAA9909</t>
+          <t>36999</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -7017,7 +6987,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>BAA9909</t>
+          <t>34760</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -7044,7 +7014,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>BSU1405</t>
+          <t>34760</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -7071,7 +7041,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>34760</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -7098,7 +7068,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>34760</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -7125,7 +7095,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>BAA9909</t>
+          <t>34760</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -7152,7 +7122,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>34760</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -7179,7 +7149,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>34760</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -7206,7 +7176,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>34760</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -7233,7 +7203,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>34760</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -7260,7 +7230,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>BAA9909</t>
+          <t>71804</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -7287,7 +7257,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>BSU1405</t>
+          <t>71804</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -7314,7 +7284,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>71804</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -7341,7 +7311,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>71804</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -7368,7 +7338,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>BAA9909</t>
+          <t>71804</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -7395,7 +7365,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>71804</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -7422,7 +7392,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>71804</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -7449,7 +7419,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>71804</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -7476,7 +7446,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>71804</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -7503,7 +7473,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>BSU1405</t>
+          <t>79508</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -7530,7 +7500,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>79508</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -7557,7 +7527,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>BSU4500</t>
+          <t>79508</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -7584,7 +7554,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>79508</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -7611,7 +7581,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>79508</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -7638,7 +7608,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>79508</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -7665,7 +7635,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>79508</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -7692,7 +7662,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>75584</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -7719,7 +7689,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>BSU4500</t>
+          <t>75584</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -7746,7 +7716,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>75584</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -7773,7 +7743,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>75584</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -7800,7 +7770,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>75584</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -7827,7 +7797,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>75584</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -7854,7 +7824,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>75584</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -7881,7 +7851,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>BSTA5000</t>
+          <t>33778</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -7908,7 +7878,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>BSTA5000</t>
+          <t>33778</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -7935,7 +7905,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>BSTA5000</t>
+          <t>33778</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -7960,11 +7930,6 @@
           <t>A55</t>
         </is>
       </c>
-      <c r="C280" t="inlineStr">
-        <is>
-          <t>BAA9909</t>
-        </is>
-      </c>
       <c r="D280" t="inlineStr">
         <is>
           <t>01/01/2026</t>
@@ -7987,11 +7952,6 @@
           <t>A52</t>
         </is>
       </c>
-      <c r="C281" t="inlineStr">
-        <is>
-          <t>DIP010</t>
-        </is>
-      </c>
       <c r="D281" t="inlineStr">
         <is>
           <t>01/01/2026</t>
@@ -8016,7 +7976,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>BSU4500</t>
+          <t>75405</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -8043,7 +8003,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>75405</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -8070,7 +8030,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>BAA9909</t>
+          <t>75405</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -8097,7 +8057,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>75405</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -8124,7 +8084,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>75405</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -8151,7 +8111,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>75405</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -8178,7 +8138,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>BSU4500</t>
+          <t>75291</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -8205,7 +8165,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>75291</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -8232,7 +8192,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>BAA9909</t>
+          <t>75291</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -8259,7 +8219,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>75291</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -8286,7 +8246,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>75291</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -8313,7 +8273,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>75291</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -8340,7 +8300,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>BSU4500</t>
+          <t>75206</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -8367,7 +8327,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>75206</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -8394,7 +8354,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>75206</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -8421,7 +8381,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>BSU9095</t>
+          <t>75206</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -8448,7 +8408,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>75344</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -8475,7 +8435,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>BSU4500</t>
+          <t>75344</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -8502,7 +8462,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>BSU4500</t>
+          <t>75344</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -8529,7 +8489,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>75344</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -8556,7 +8516,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>BSEA2202</t>
+          <t>75344</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -8583,7 +8543,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>75344</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -8610,7 +8570,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>75344</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -8637,7 +8597,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>BSTA1002</t>
+          <t>79179</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -8664,7 +8624,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>BSTA4110</t>
+          <t>79179</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -8691,7 +8651,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>BSTA4110</t>
+          <t>79179</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -8718,7 +8678,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>79179</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -8745,7 +8705,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>BSTA4330</t>
+          <t>36135</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -8772,7 +8732,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>36135</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -8799,7 +8759,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>BSTA4330</t>
+          <t>36135</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -8826,7 +8786,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>BSTA4330</t>
+          <t>36135</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -8853,7 +8813,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>BSTA4330</t>
+          <t>36135</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -8880,7 +8840,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>BSTA4330</t>
+          <t>36135</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -8907,7 +8867,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>BSU4500</t>
+          <t>31997</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -8934,7 +8894,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>31997</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -8961,7 +8921,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>31997</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -8988,7 +8948,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>31997</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -9015,7 +8975,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>BAA9909</t>
+          <t>31997</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -9042,7 +9002,7 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>BAA9909</t>
+          <t>31997</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -9069,7 +9029,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>BSU4500</t>
+          <t>70405</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -9096,7 +9056,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>BSU4500</t>
+          <t>70405</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -9123,7 +9083,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>70405</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -9150,7 +9110,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>BSU4700</t>
+          <t>70405</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -9177,7 +9137,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>70405</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -9204,7 +9164,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>BAA9909</t>
+          <t>70405</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -9231,7 +9191,7 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>70405</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -9256,11 +9216,6 @@
           <t>E06b</t>
         </is>
       </c>
-      <c r="C328" t="inlineStr">
-        <is>
-          <t>BSU4500</t>
-        </is>
-      </c>
       <c r="D328" t="inlineStr">
         <is>
           <t>01/01/2026</t>
@@ -9283,11 +9238,6 @@
           <t>E05b</t>
         </is>
       </c>
-      <c r="C329" t="inlineStr">
-        <is>
-          <t>BSU4500</t>
-        </is>
-      </c>
       <c r="D329" t="inlineStr">
         <is>
           <t>01/01/2026</t>
@@ -9310,11 +9260,6 @@
           <t>A112</t>
         </is>
       </c>
-      <c r="C330" t="inlineStr">
-        <is>
-          <t>BAA9909</t>
-        </is>
-      </c>
       <c r="D330" t="inlineStr">
         <is>
           <t>01/01/2026</t>
@@ -9339,7 +9284,7 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>BAA9909</t>
+          <t>70539</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -9366,7 +9311,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>BSTA4010</t>
+          <t>70539</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -9393,7 +9338,7 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>BAA9909</t>
+          <t>70539</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -9420,7 +9365,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>BSTA4010</t>
+          <t>70539</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -9447,7 +9392,7 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>BSTA4010</t>
+          <t>70539</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -9474,7 +9419,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>78851</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -9501,7 +9446,7 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>BAA9909</t>
+          <t>78851</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
@@ -9528,7 +9473,7 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>78851</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
@@ -9555,7 +9500,7 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>78851</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -9582,7 +9527,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>BAA9909</t>
+          <t>78851</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
@@ -9609,7 +9554,7 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>76453</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -9636,7 +9581,7 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>BAA9909</t>
+          <t>76327</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
@@ -9663,7 +9608,7 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>BSU4500</t>
+          <t>76327</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
@@ -9690,7 +9635,7 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>BSU4500</t>
+          <t>76327</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
@@ -9717,7 +9662,7 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>76327</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
@@ -9744,7 +9689,7 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>DIP007</t>
+          <t>76327</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
@@ -9771,7 +9716,7 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>BSU4700</t>
+          <t>76327</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
@@ -9798,7 +9743,7 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>BAA9909</t>
+          <t>76327</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
@@ -9825,7 +9770,7 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>BSU4500</t>
+          <t>38611</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
@@ -9852,7 +9797,7 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>BSU4500</t>
+          <t>38611</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
@@ -9879,7 +9824,7 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>38611</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
@@ -9906,7 +9851,7 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>38611</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
@@ -9933,7 +9878,7 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>BSU4700</t>
+          <t>38611</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
@@ -9960,7 +9905,7 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>BAA9909</t>
+          <t>38611</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
@@ -9987,7 +9932,7 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>38611</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
@@ -10014,7 +9959,7 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>BSEA2810</t>
+          <t>76311</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
@@ -10041,7 +9986,7 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>BSU4500</t>
+          <t>76311</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
@@ -10068,7 +10013,7 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>BSU4500</t>
+          <t>76311</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
@@ -10095,7 +10040,7 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>76311</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
@@ -10122,7 +10067,7 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>BSU4700</t>
+          <t>76311</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
@@ -10149,7 +10094,7 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>76311</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
@@ -10176,7 +10121,7 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>BAA9909</t>
+          <t>75373</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
@@ -10203,7 +10148,7 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>BSU4500</t>
+          <t>75373</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
@@ -10230,7 +10175,7 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>BSU4500</t>
+          <t>75373</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
@@ -10257,7 +10202,7 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>75373</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
@@ -10284,7 +10229,7 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>BSU4700</t>
+          <t>75373</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
@@ -10311,7 +10256,7 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>BAA9909</t>
+          <t>75373</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
@@ -10338,7 +10283,7 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>BAA9909</t>
+          <t>75373</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
@@ -10365,7 +10310,7 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>BSU1405</t>
+          <t>33601</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
@@ -10392,7 +10337,7 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>33601</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
@@ -10419,7 +10364,7 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>BSU4500</t>
+          <t>33601</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
@@ -10446,7 +10391,7 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>33601</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
@@ -10473,7 +10418,7 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>BAA9909</t>
+          <t>33601</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
@@ -10500,7 +10445,7 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>33601</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
@@ -10527,7 +10472,7 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>BAA9909</t>
+          <t>33601</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
@@ -10554,7 +10499,7 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>33601</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
@@ -10581,7 +10526,7 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>BSU1405</t>
+          <t>31294</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
@@ -10608,7 +10553,7 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>31294</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
@@ -10635,7 +10580,7 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>31294</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
@@ -10662,7 +10607,7 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>BAA9909</t>
+          <t>31294</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
@@ -10689,7 +10634,7 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>31294</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
@@ -10716,7 +10661,7 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>BSCP1407</t>
+          <t>31294</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
@@ -10743,7 +10688,7 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>BSCP1407</t>
+          <t>31294</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
@@ -10770,7 +10715,7 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>78261</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
@@ -10797,7 +10742,7 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>BSU9208</t>
+          <t>78261</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
@@ -10824,7 +10769,7 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>78261</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
@@ -10851,7 +10796,7 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>BSU9208</t>
+          <t>78261</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
@@ -10878,7 +10823,7 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>BAA9909</t>
+          <t>34944</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
@@ -10905,7 +10850,7 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>34944</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
@@ -10932,7 +10877,7 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>34944</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
@@ -10959,7 +10904,7 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>34944</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
@@ -10986,7 +10931,7 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>34944</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
@@ -11013,7 +10958,7 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>34944</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
@@ -11040,7 +10985,7 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>BAA9909</t>
+          <t>35167</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
@@ -11067,7 +11012,7 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>35167</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
@@ -11094,7 +11039,7 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>BSU4500</t>
+          <t>35167</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
@@ -11121,7 +11066,7 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>35167</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
@@ -11148,7 +11093,7 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>35167</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
@@ -11175,7 +11120,7 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>35167</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
@@ -11202,7 +11147,7 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>35167</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
@@ -11229,7 +11174,7 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>BSEA14081</t>
+          <t>30648</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
@@ -11256,7 +11201,7 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>BSEA14081</t>
+          <t>30648</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
@@ -11283,7 +11228,7 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>BSEA14081</t>
+          <t>30648</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
@@ -11310,7 +11255,7 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>BSEA14081</t>
+          <t>30648</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
@@ -11337,7 +11282,7 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>75420</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
@@ -11364,7 +11309,7 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>BSU4500</t>
+          <t>75420</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
@@ -11391,7 +11336,7 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>75420</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
@@ -11418,7 +11363,7 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>BAA9909</t>
+          <t>75420</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
@@ -11445,7 +11390,7 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>BSOP3310</t>
+          <t>75420</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
@@ -11472,7 +11417,7 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>BAA9909</t>
+          <t>75420</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
@@ -11499,7 +11444,7 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>75420</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
@@ -11526,7 +11471,7 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>BSMP3700</t>
+          <t>31101</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
@@ -11553,7 +11498,7 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>BSU4500</t>
+          <t>31101</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
@@ -11580,7 +11525,7 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>BSMP3700</t>
+          <t>31101</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
@@ -11607,7 +11552,7 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>BSMP3700</t>
+          <t>31101</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
@@ -11634,7 +11579,7 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>31101</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
@@ -11661,7 +11606,7 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>BAA9909</t>
+          <t>31101</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
@@ -11688,7 +11633,7 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>31101</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
@@ -11715,7 +11660,7 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>BSU4500</t>
+          <t>34809</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
@@ -11742,7 +11687,7 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>34809</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
@@ -11769,7 +11714,7 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>BSMP1401</t>
+          <t>34809</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
@@ -11796,7 +11741,7 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>BAA9909</t>
+          <t>34809</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
@@ -11823,7 +11768,7 @@
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>34809</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
@@ -11850,7 +11795,7 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>BSTA1002</t>
+          <t>35716</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
@@ -11877,7 +11822,7 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>BSTA1003</t>
+          <t>35716</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
@@ -11904,7 +11849,7 @@
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>35716</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
@@ -11931,7 +11876,7 @@
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>BSTA1003</t>
+          <t>35716</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
@@ -11958,7 +11903,7 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>BSOP1901</t>
+          <t>75578</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
@@ -11985,7 +11930,7 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>BSTA4110</t>
+          <t>75578</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
@@ -12012,7 +11957,7 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>BSTA1002</t>
+          <t>75578</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
@@ -12039,7 +11984,7 @@
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>BSTA1002</t>
+          <t>75578</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
@@ -12066,7 +12011,7 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>BSTA1002</t>
+          <t>75578</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
@@ -12091,11 +12036,6 @@
           <t>E01</t>
         </is>
       </c>
-      <c r="C433" t="inlineStr">
-        <is>
-          <t>DIP010</t>
-        </is>
-      </c>
       <c r="D433" t="inlineStr">
         <is>
           <t>01/01/2026</t>
@@ -12118,11 +12058,6 @@
           <t>A71</t>
         </is>
       </c>
-      <c r="C434" t="inlineStr">
-        <is>
-          <t>DIP010</t>
-        </is>
-      </c>
       <c r="D434" t="inlineStr">
         <is>
           <t>01/01/2026</t>
@@ -12147,7 +12082,7 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>70555</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
@@ -12174,7 +12109,7 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>70555</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
@@ -12201,7 +12136,7 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>BAA9909</t>
+          <t>70555</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
@@ -12228,7 +12163,7 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>BAA9909</t>
+          <t>70555</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
@@ -12255,7 +12190,7 @@
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>70555</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
@@ -12282,7 +12217,7 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>BSOP1901</t>
+          <t>71845</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
@@ -12309,7 +12244,7 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>71845</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
@@ -12336,7 +12271,7 @@
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>BSOP1901</t>
+          <t>71845</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
@@ -12363,7 +12298,7 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>BSOP1901</t>
+          <t>71845</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
@@ -12390,7 +12325,7 @@
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>BAA9909</t>
+          <t>71845</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
@@ -12417,7 +12352,7 @@
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>BSU1405</t>
+          <t>72328</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
@@ -12444,7 +12379,7 @@
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>72328</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
@@ -12471,7 +12406,7 @@
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>BSU1405</t>
+          <t>72328</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
@@ -12498,7 +12433,7 @@
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>78857</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
@@ -12525,7 +12460,7 @@
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>BSOP2214</t>
+          <t>78857</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
@@ -12552,7 +12487,7 @@
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>78857</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
@@ -12579,7 +12514,7 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>78857</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
@@ -12606,7 +12541,7 @@
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>BAA9909</t>
+          <t>78857</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
@@ -12631,11 +12566,6 @@
           <t>A82</t>
         </is>
       </c>
-      <c r="C453" t="inlineStr">
-        <is>
-          <t>BSU7200</t>
-        </is>
-      </c>
       <c r="D453" t="inlineStr">
         <is>
           <t>01/01/2026</t>
@@ -12658,11 +12588,6 @@
           <t>A44</t>
         </is>
       </c>
-      <c r="C454" t="inlineStr">
-        <is>
-          <t>BSEA1410</t>
-        </is>
-      </c>
       <c r="D454" t="inlineStr">
         <is>
           <t>01/01/2026</t>
@@ -12685,11 +12610,6 @@
           <t>A39</t>
         </is>
       </c>
-      <c r="C455" t="inlineStr">
-        <is>
-          <t>BSEA1410</t>
-        </is>
-      </c>
       <c r="D455" t="inlineStr">
         <is>
           <t>01/01/2026</t>
@@ -12712,11 +12632,6 @@
           <t>A07c</t>
         </is>
       </c>
-      <c r="C456" t="inlineStr">
-        <is>
-          <t>BSU7200</t>
-        </is>
-      </c>
       <c r="D456" t="inlineStr">
         <is>
           <t>01/01/2026</t>
@@ -12741,7 +12656,7 @@
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>BAA9909</t>
+          <t>72329</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
@@ -12768,7 +12683,7 @@
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>BSTA4800-1</t>
+          <t>72329</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
@@ -12795,7 +12710,7 @@
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>72329</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
@@ -12822,7 +12737,7 @@
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>DIP010</t>
+          <t>72329</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
@@ -12849,7 +12764,7 @@
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>72329</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
@@ -12876,7 +12791,7 @@
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>72329</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
@@ -12903,7 +12818,7 @@
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>72329</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
@@ -12930,7 +12845,7 @@
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>BSU7200</t>
+          <t>72329</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">

--- a/script/templates/WePartyInterface_BS.xlsx
+++ b/script/templates/WePartyInterface_BS.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E464"/>
+  <dimension ref="A1:E447"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5468,12 +5468,17 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>OB_STG_BSTA4111</t>
+          <t>OB_STG_BSMP3020</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>S16</t>
+          <t>E05</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>79354</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -5490,12 +5495,17 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>OB_STG_BSTA4111</t>
+          <t>OB_STG_BSMP3020</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>S15</t>
+          <t>E01</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>79354</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -5512,12 +5522,17 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>OB_STG_BSTA4111</t>
+          <t>OB_STG_BSMP3020</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>S14</t>
+          <t>A98</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>79354</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -5534,12 +5549,17 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>OB_STG_BSTA4111</t>
+          <t>OB_STG_BSMP3020</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>S13</t>
+          <t>A97</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>79354</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -5556,12 +5576,17 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>OB_STG_BSTA4111</t>
+          <t>OB_STG_BSMP3020</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>A96</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>79354</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -5578,12 +5603,17 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>OB_STG_BSTA4111</t>
+          <t>OB_STG_BSMP3020</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>E01</t>
+          <t>A82b</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>79354</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -5605,7 +5635,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>E05</t>
+          <t>A59b</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -5632,7 +5662,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>E01</t>
+          <t>A09c</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -5659,7 +5689,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>A98</t>
+          <t>A07b</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -5681,17 +5711,17 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP3020</t>
+          <t>OB_STG_BSEA2500</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>A97</t>
+          <t>E07</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>79354</t>
+          <t>78392</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -5708,17 +5738,17 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP3020</t>
+          <t>OB_STG_BSEA2500</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>A96</t>
+          <t>E01</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>79354</t>
+          <t>78392</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -5735,17 +5765,17 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP3020</t>
+          <t>OB_STG_BSEA2500</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>A82b</t>
+          <t>A83b</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>79354</t>
+          <t>78392</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -5762,17 +5792,17 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP3020</t>
+          <t>OB_STG_BSEA2500</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>A59b</t>
+          <t>A82</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>79354</t>
+          <t>78392</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -5789,17 +5819,17 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP3020</t>
+          <t>OB_STG_BSEA2500</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>A09c</t>
+          <t>A09</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>79354</t>
+          <t>78392</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -5816,17 +5846,17 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP3020</t>
+          <t>OB_STG_BSEA2500</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>A07b</t>
+          <t>A07</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>79354</t>
+          <t>78392</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -5843,17 +5873,17 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA2500</t>
+          <t>OB_STG_BSMP2610</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>E07</t>
+          <t>E01</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>78392</t>
+          <t>34295</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -5870,17 +5900,17 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA2500</t>
+          <t>OB_STG_BSMP2610</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>E01</t>
+          <t>A83</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>78392</t>
+          <t>34295</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -5897,17 +5927,17 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA2500</t>
+          <t>OB_STG_BSMP2610</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>A83b</t>
+          <t>A111</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>78392</t>
+          <t>34295</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -5924,17 +5954,17 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA2500</t>
+          <t>OB_STG_BSMP2610</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>A82</t>
+          <t>A110</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>78392</t>
+          <t>34295</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -5951,17 +5981,17 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA2500</t>
+          <t>OB_STG_BSMP2610</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>A09</t>
+          <t>A10c</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>78392</t>
+          <t>34295</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -5978,17 +6008,17 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA2500</t>
+          <t>OB_STG_BSMP2610</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>A07</t>
+          <t>A109</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>78392</t>
+          <t>34295</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -6005,17 +6035,17 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP2610</t>
+          <t>OB_STG_BSEA2600</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>E01</t>
+          <t>E05</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>34295</t>
+          <t>30235</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -6032,17 +6062,17 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP2610</t>
+          <t>OB_STG_BSEA2600</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>A83</t>
+          <t>E01</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>34295</t>
+          <t>30235</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -6059,17 +6089,17 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP2610</t>
+          <t>OB_STG_BSEA2600</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>A111</t>
+          <t>A83</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>34295</t>
+          <t>30235</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -6086,17 +6116,17 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP2610</t>
+          <t>OB_STG_BSEA2600</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>A110</t>
+          <t>A82</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>34295</t>
+          <t>30235</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -6113,7 +6143,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP2610</t>
+          <t>OB_STG_BSEA2600</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -6123,7 +6153,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>34295</t>
+          <t>30235</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -6140,17 +6170,17 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP2610</t>
+          <t>OB_STG_BSEA2600</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>A109</t>
+          <t>A09</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>34295</t>
+          <t>30235</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -6172,7 +6202,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>E05</t>
+          <t>A07</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -6194,17 +6224,17 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA2600</t>
+          <t>OB_STG_BSTA4100</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>E01</t>
+          <t>S33</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>30235</t>
+          <t>35946</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -6221,17 +6251,17 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA2600</t>
+          <t>OB_STG_BSTA4100</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>A83</t>
+          <t>E03</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>30235</t>
+          <t>35946</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -6248,17 +6278,17 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA2600</t>
+          <t>OB_STG_BSTA4100</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>A82</t>
+          <t>E01</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>30235</t>
+          <t>35946</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -6275,17 +6305,17 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA2600</t>
+          <t>OB_STG_BSTA4100</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>A10c</t>
+          <t>A90</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>30235</t>
+          <t>35946</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -6302,17 +6332,17 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA2600</t>
+          <t>OB_STG_BSTA4100</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>A09</t>
+          <t>A38</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>30235</t>
+          <t>35946</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -6329,17 +6359,17 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA2600</t>
+          <t>OB_STG_BSTA4100</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>A07</t>
+          <t>A11</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>30235</t>
+          <t>35946</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -6356,17 +6386,17 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>OB_STG_BSTA4100</t>
+          <t>OB_STG_BSCP1810</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>S33</t>
+          <t>E07c</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>35946</t>
+          <t>32815</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -6383,17 +6413,17 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>OB_STG_BSTA4100</t>
+          <t>OB_STG_BSCP1810</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>E03</t>
+          <t>E03b</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>35946</t>
+          <t>32815</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -6410,7 +6440,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>OB_STG_BSTA4100</t>
+          <t>OB_STG_BSCP1810</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -6420,7 +6450,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>35946</t>
+          <t>32815</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -6437,17 +6467,17 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>OB_STG_BSTA4100</t>
+          <t>OB_STG_BSCP1810</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>A90</t>
+          <t>A83b</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>35946</t>
+          <t>32815</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -6464,17 +6494,17 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>OB_STG_BSTA4100</t>
+          <t>OB_STG_BSCP1810</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>A38</t>
+          <t>A10</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>35946</t>
+          <t>32815</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -6491,17 +6521,17 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>OB_STG_BSTA4100</t>
+          <t>OB_STG_BSCP1810</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>A11</t>
+          <t>A07c</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>35946</t>
+          <t>32815</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -6518,17 +6548,17 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP1810</t>
+          <t>OB_STG_BSCS0510</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>E07c</t>
+          <t>E07b</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>32815</t>
+          <t>33479</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -6545,7 +6575,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP1810</t>
+          <t>OB_STG_BSCS0510</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -6555,7 +6585,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>32815</t>
+          <t>33479</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -6572,7 +6602,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP1810</t>
+          <t>OB_STG_BSCS0510</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -6582,7 +6612,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>32815</t>
+          <t>33479</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -6599,17 +6629,17 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP1810</t>
+          <t>OB_STG_BSCS0510</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>A83b</t>
+          <t>A30</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>32815</t>
+          <t>33479</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -6626,17 +6656,17 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP1810</t>
+          <t>OB_STG_BSCS0510</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>A10</t>
+          <t>A29</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>32815</t>
+          <t>33479</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -6653,17 +6683,17 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP1810</t>
+          <t>OB_STG_BSOP3310</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>A07c</t>
+          <t>E12</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>32815</t>
+          <t>36999</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -6680,17 +6710,17 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS0510</t>
+          <t>OB_STG_BSOP3310</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>E07b</t>
+          <t>E05</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>33479</t>
+          <t>36999</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -6707,17 +6737,17 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS0510</t>
+          <t>OB_STG_BSOP3310</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>E03b</t>
+          <t>E01</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>33479</t>
+          <t>36999</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -6734,17 +6764,17 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS0510</t>
+          <t>OB_STG_BSOP3310</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>E01</t>
+          <t>A83</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>33479</t>
+          <t>36999</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -6761,17 +6791,17 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS0510</t>
+          <t>OB_STG_BSOP3310</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>A30</t>
+          <t>A56</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>33479</t>
+          <t>36999</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -6788,17 +6818,17 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS0510</t>
+          <t>OB_STG_BSOP3310</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>A29</t>
+          <t>A55</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>33479</t>
+          <t>36999</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -6815,17 +6845,17 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>OB_STG_BSOP3310</t>
+          <t>OB_STG_BSCP2400</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>E12</t>
+          <t>S59b</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>36999</t>
+          <t>34760</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -6842,17 +6872,17 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>OB_STG_BSOP3310</t>
+          <t>OB_STG_BSCP2400</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>E05</t>
+          <t>S47b</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>36999</t>
+          <t>34760</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -6869,17 +6899,17 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>OB_STG_BSOP3310</t>
+          <t>OB_STG_BSCP2400</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>E01</t>
+          <t>E07b</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>36999</t>
+          <t>34760</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -6896,17 +6926,17 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>OB_STG_BSOP3310</t>
+          <t>OB_STG_BSCP2400</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>A83</t>
+          <t>E01</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>36999</t>
+          <t>34760</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -6923,17 +6953,17 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>OB_STG_BSOP3310</t>
+          <t>OB_STG_BSCP2400</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>A56</t>
+          <t>A83</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>36999</t>
+          <t>34760</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -6950,17 +6980,17 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>OB_STG_BSOP3310</t>
+          <t>OB_STG_BSCP2400</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>A55</t>
+          <t>A82b</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>36999</t>
+          <t>34760</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -6982,7 +7012,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>S59b</t>
+          <t>A08</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -7009,7 +7039,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>S47b</t>
+          <t>A07b</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -7036,7 +7066,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>E07b</t>
+          <t>A04</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -7058,17 +7088,17 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP2400</t>
+          <t>OB_STG_BSCP0208</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>E01</t>
+          <t>S59b</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>34760</t>
+          <t>71804</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -7085,17 +7115,17 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP2400</t>
+          <t>OB_STG_BSCP0208</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>A83</t>
+          <t>S47b</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>34760</t>
+          <t>71804</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -7112,17 +7142,17 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP2400</t>
+          <t>OB_STG_BSCP0208</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>A82b</t>
+          <t>E07b</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>34760</t>
+          <t>71804</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -7139,17 +7169,17 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP2400</t>
+          <t>OB_STG_BSCP0208</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>A08</t>
+          <t>E01</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>34760</t>
+          <t>71804</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -7166,17 +7196,17 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP2400</t>
+          <t>OB_STG_BSCP0208</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>A07b</t>
+          <t>A83</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>34760</t>
+          <t>71804</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -7193,17 +7223,17 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP2400</t>
+          <t>OB_STG_BSCP0208</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>A04</t>
+          <t>A82b</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>34760</t>
+          <t>71804</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -7225,7 +7255,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>S59b</t>
+          <t>A08</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -7252,7 +7282,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>S47b</t>
+          <t>A07b</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -7279,7 +7309,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>E07b</t>
+          <t>A04</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -7301,17 +7331,17 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP0208</t>
+          <t>OB_STG_BSCP3500</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>E01</t>
+          <t>S47b</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>71804</t>
+          <t>79508</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -7328,17 +7358,17 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP0208</t>
+          <t>OB_STG_BSCP3500</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>A83</t>
+          <t>E22</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>71804</t>
+          <t>79508</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -7355,17 +7385,17 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP0208</t>
+          <t>OB_STG_BSCP3500</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>A82b</t>
+          <t>E05</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>71804</t>
+          <t>79508</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -7382,17 +7412,17 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP0208</t>
+          <t>OB_STG_BSCP3500</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>A08</t>
+          <t>E01</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>71804</t>
+          <t>79508</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -7409,17 +7439,17 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP0208</t>
+          <t>OB_STG_BSCP3500</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>A07b</t>
+          <t>A82</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>71804</t>
+          <t>79508</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -7436,17 +7466,17 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP0208</t>
+          <t>OB_STG_BSCP3500</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>A04</t>
+          <t>A07</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>71804</t>
+          <t>79508</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -7468,7 +7498,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>S47b</t>
+          <t>A05</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -7490,17 +7520,17 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP3500</t>
+          <t>OB_STG_BSCP1800</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>E22</t>
+          <t>E07</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>79508</t>
+          <t>75584</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -7517,7 +7547,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP3500</t>
+          <t>OB_STG_BSCP1800</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -7527,7 +7557,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>79508</t>
+          <t>75584</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -7544,17 +7574,17 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP3500</t>
+          <t>OB_STG_BSCP1800</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>E01</t>
+          <t>E03</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>79508</t>
+          <t>75584</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -7571,17 +7601,17 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP3500</t>
+          <t>OB_STG_BSCP1800</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>A82</t>
+          <t>E01</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>79508</t>
+          <t>75584</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -7598,17 +7628,17 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP3500</t>
+          <t>OB_STG_BSCP1800</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>A07</t>
+          <t>A82</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>79508</t>
+          <t>75584</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -7625,17 +7655,17 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP3500</t>
+          <t>OB_STG_BSCP1800</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>A05</t>
+          <t>A101b</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>79508</t>
+          <t>75584</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -7657,7 +7687,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>E07</t>
+          <t>A07</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -7679,17 +7709,17 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP1800</t>
+          <t>OB_STG_BSTA5000</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>E05</t>
+          <t>S55</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>75584</t>
+          <t>33778</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -7706,17 +7736,17 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP1800</t>
+          <t>OB_STG_BSTA5000</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>E03</t>
+          <t>S54</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>75584</t>
+          <t>33778</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -7733,17 +7763,17 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP1800</t>
+          <t>OB_STG_BSTA5000</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>E01</t>
+          <t>S53</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>75584</t>
+          <t>33778</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -7760,17 +7790,17 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP1800</t>
+          <t>OB_STG_BSOP3100</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>A82</t>
+          <t>E05</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>75584</t>
+          <t>75405</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -7787,17 +7817,17 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP1800</t>
+          <t>OB_STG_BSOP3100</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>A101b</t>
+          <t>E01</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>75584</t>
+          <t>75405</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -7814,17 +7844,17 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP1800</t>
+          <t>OB_STG_BSOP3100</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>A07</t>
+          <t>A83</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>75584</t>
+          <t>75405</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -7841,17 +7871,17 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>OB_STG_BSTA5000</t>
+          <t>OB_STG_BSOP3100</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>S55</t>
+          <t>A82</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>33778</t>
+          <t>75405</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -7868,17 +7898,17 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>OB_STG_BSTA5000</t>
+          <t>OB_STG_BSOP3100</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>S54</t>
+          <t>A54</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>33778</t>
+          <t>75405</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -7895,17 +7925,17 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>OB_STG_BSTA5000</t>
+          <t>OB_STG_BSOP3100</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>S53</t>
+          <t>A07</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>33778</t>
+          <t>75405</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -7922,12 +7952,17 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>OB_STG_BAA9908</t>
+          <t>OB_STG_BSOP3600</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>A55</t>
+          <t>E05</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>75291</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -7944,12 +7979,17 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>OB_STG_BAA9908</t>
+          <t>OB_STG_BSOP3600</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>A52</t>
+          <t>E01</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>75291</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -7966,17 +8006,17 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>OB_STG_BSOP3100</t>
+          <t>OB_STG_BSOP3600</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>E05</t>
+          <t>A83</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>75405</t>
+          <t>75291</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -7993,17 +8033,17 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>OB_STG_BSOP3100</t>
+          <t>OB_STG_BSOP3600</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>E01</t>
+          <t>A82</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>75405</t>
+          <t>75291</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -8020,17 +8060,17 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>OB_STG_BSOP3100</t>
+          <t>OB_STG_BSOP3600</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>A83</t>
+          <t>A53</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>75405</t>
+          <t>75291</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -8047,17 +8087,17 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>OB_STG_BSOP3100</t>
+          <t>OB_STG_BSOP3600</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>A82</t>
+          <t>A07</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>75405</t>
+          <t>75291</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -8074,17 +8114,17 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>OB_STG_BSOP3100</t>
+          <t>OB_STG_BSU9095</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>A54</t>
+          <t>E05</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>75405</t>
+          <t>75206</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -8101,17 +8141,17 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>OB_STG_BSOP3100</t>
+          <t>OB_STG_BSU9095</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>A07</t>
+          <t>E07</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>75405</t>
+          <t>75206</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -8128,17 +8168,17 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>OB_STG_BSOP3600</t>
+          <t>OB_STG_BSU9095</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>E05</t>
+          <t>E04</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>75291</t>
+          <t>75206</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -8155,17 +8195,17 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>OB_STG_BSOP3600</t>
+          <t>OB_STG_BSU9095</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>E01</t>
+          <t>A113</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>75291</t>
+          <t>75206</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -8182,17 +8222,17 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>OB_STG_BSOP3600</t>
+          <t>OB_STG_BSEA2202</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>A83</t>
+          <t>E15</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>75291</t>
+          <t>75344</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -8209,17 +8249,17 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>OB_STG_BSOP3600</t>
+          <t>OB_STG_BSEA2202</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>A82</t>
+          <t>E06</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>75291</t>
+          <t>75344</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -8236,17 +8276,17 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>OB_STG_BSOP3600</t>
+          <t>OB_STG_BSEA2202</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>A53</t>
+          <t>E05</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>75291</t>
+          <t>75344</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -8263,17 +8303,17 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>OB_STG_BSOP3600</t>
+          <t>OB_STG_BSEA2202</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>A07</t>
+          <t>A82e</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>75291</t>
+          <t>75344</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -8290,17 +8330,17 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>OB_STG_BSU9095</t>
+          <t>OB_STG_BSEA2202</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>E05</t>
+          <t>A106</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>75206</t>
+          <t>75344</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -8317,17 +8357,17 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>OB_STG_BSU9095</t>
+          <t>OB_STG_BSEA2202</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>E07</t>
+          <t>A104</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>75206</t>
+          <t>75344</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -8344,17 +8384,17 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>OB_STG_BSU9095</t>
+          <t>OB_STG_BSEA2202</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>E04</t>
+          <t>A07</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>75206</t>
+          <t>75344</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -8371,17 +8411,17 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>OB_STG_BSU9095</t>
+          <t>OB_STG_BSTA4110</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>A113</t>
+          <t>S26</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>75206</t>
+          <t>79179</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -8398,17 +8438,17 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA2202</t>
+          <t>OB_STG_BSTA4110</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>E15</t>
+          <t>S25</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>75344</t>
+          <t>79179</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -8425,17 +8465,17 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA2202</t>
+          <t>OB_STG_BSTA4110</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>E06</t>
+          <t>S24b</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>75344</t>
+          <t>79179</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -8452,17 +8492,17 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA2202</t>
+          <t>OB_STG_BSTA4110</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>E05</t>
+          <t>E01</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>75344</t>
+          <t>79179</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -8479,17 +8519,17 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA2202</t>
+          <t>OB_STG_BSTA4330</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>A82e</t>
+          <t>S31b</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>75344</t>
+          <t>36135</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -8506,17 +8546,17 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA2202</t>
+          <t>OB_STG_BSTA4330</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>A106</t>
+          <t>E01</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>75344</t>
+          <t>36135</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -8533,17 +8573,17 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA2202</t>
+          <t>OB_STG_BSTA4330</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>A104</t>
+          <t>A91</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>75344</t>
+          <t>36135</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -8560,17 +8600,17 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA2202</t>
+          <t>OB_STG_BSTA4330</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>A07</t>
+          <t>A16</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>75344</t>
+          <t>36135</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -8587,17 +8627,17 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>OB_STG_BSTA4110</t>
+          <t>OB_STG_BSTA4330</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>S26</t>
+          <t>A15</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>79179</t>
+          <t>36135</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -8614,17 +8654,17 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>OB_STG_BSTA4110</t>
+          <t>OB_STG_BSTA4330</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>S25</t>
+          <t>A14</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>79179</t>
+          <t>36135</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -8641,17 +8681,17 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>OB_STG_BSTA4110</t>
+          <t>OB_STG_BSMP1310</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>S24b</t>
+          <t>E05</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>79179</t>
+          <t>31997</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -8668,7 +8708,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>OB_STG_BSTA4110</t>
+          <t>OB_STG_BSMP1310</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -8678,7 +8718,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>79179</t>
+          <t>31997</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -8695,17 +8735,17 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>OB_STG_BSTA4330</t>
+          <t>OB_STG_BSMP1310</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>S31b</t>
+          <t>A89</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>36135</t>
+          <t>31997</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -8722,17 +8762,17 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>OB_STG_BSTA4330</t>
+          <t>OB_STG_BSMP1310</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>E01</t>
+          <t>A82</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>36135</t>
+          <t>31997</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -8749,17 +8789,17 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>OB_STG_BSTA4330</t>
+          <t>OB_STG_BSMP1310</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>A91</t>
+          <t>A26</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>36135</t>
+          <t>31997</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -8776,17 +8816,17 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>OB_STG_BSTA4330</t>
+          <t>OB_STG_BSMP1310</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>A16</t>
+          <t>A10b</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>36135</t>
+          <t>31997</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -8803,17 +8843,17 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>OB_STG_BSTA4330</t>
+          <t>OB_STG_BSEA2210</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>A15</t>
+          <t>E06</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>36135</t>
+          <t>70405</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -8830,17 +8870,17 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>OB_STG_BSTA4330</t>
+          <t>OB_STG_BSEA2210</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>A14</t>
+          <t>E05</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>36135</t>
+          <t>70405</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -8857,17 +8897,17 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP1310</t>
+          <t>OB_STG_BSEA2210</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>E05</t>
+          <t>A92</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>31997</t>
+          <t>70405</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -8884,17 +8924,17 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP1310</t>
+          <t>OB_STG_BSEA2210</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>E01</t>
+          <t>A65b</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>31997</t>
+          <t>70405</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -8911,17 +8951,17 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP1310</t>
+          <t>OB_STG_BSEA2210</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>A89</t>
+          <t>A18</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>31997</t>
+          <t>70405</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -8938,17 +8978,17 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP1310</t>
+          <t>OB_STG_BSEA2210</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>A82</t>
+          <t>A10</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>31997</t>
+          <t>70405</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -8965,17 +9005,17 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP1310</t>
+          <t>OB_STG_BSEA2210</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>A26</t>
+          <t>A07</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>31997</t>
+          <t>70405</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -8992,17 +9032,17 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP1310</t>
+          <t>OB_STG_BSTA4010</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>A10b</t>
+          <t>E18</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>31997</t>
+          <t>70539</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -9019,17 +9059,17 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA2210</t>
+          <t>OB_STG_BSTA4010</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>E06</t>
+          <t>E16</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>70405</t>
+          <t>70539</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -9046,17 +9086,17 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA2210</t>
+          <t>OB_STG_BSTA4010</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>E05</t>
+          <t>A83</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>70405</t>
+          <t>70539</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -9073,17 +9113,17 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA2210</t>
+          <t>OB_STG_BSTA4010</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>A92</t>
+          <t>A06b</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>70405</t>
+          <t>70539</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -9100,17 +9140,17 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA2210</t>
+          <t>OB_STG_BSTA4010</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>A65b</t>
+          <t>A06</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>70405</t>
+          <t>70539</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -9127,17 +9167,17 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA2210</t>
+          <t>OB_STG_BSOP3800</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>A18</t>
+          <t>E01</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>70405</t>
+          <t>78851</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -9154,17 +9194,17 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA2210</t>
+          <t>OB_STG_BSOP3800</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>A10</t>
+          <t>A83</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>70405</t>
+          <t>78851</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -9181,17 +9221,17 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA2210</t>
+          <t>OB_STG_BSOP3800</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>A07</t>
+          <t>A82c</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>70405</t>
+          <t>78851</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -9208,12 +9248,17 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>OB_STG_BSU4500</t>
+          <t>OB_STG_BSOP3800</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>E06b</t>
+          <t>A42</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>78851</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -9230,12 +9275,17 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>OB_STG_BSU4500</t>
+          <t>OB_STG_BSOP3800</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>E05b</t>
+          <t>A10</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>78851</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -9252,12 +9302,17 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>OB_STG_BSU4500</t>
+          <t>OB_STG_BAA9911</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>A112</t>
+          <t>A61</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>76453</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -9274,17 +9329,17 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>OB_STG_BSTA4010</t>
+          <t>OB_STG_BSTR2213</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>E18</t>
+          <t>S66</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>70539</t>
+          <t>76327</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -9301,17 +9356,17 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>OB_STG_BSTA4010</t>
+          <t>OB_STG_BSTR2213</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>E16</t>
+          <t>E06</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>70539</t>
+          <t>76327</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -9328,17 +9383,17 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>OB_STG_BSTA4010</t>
+          <t>OB_STG_BSTR2213</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>A83</t>
+          <t>E05</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>70539</t>
+          <t>76327</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -9355,17 +9410,17 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>OB_STG_BSTA4010</t>
+          <t>OB_STG_BSTR2213</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>A06b</t>
+          <t>A92</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>70539</t>
+          <t>76327</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -9382,17 +9437,17 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>OB_STG_BSTA4010</t>
+          <t>OB_STG_BSTR2213</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>A06</t>
+          <t>A67b</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>70539</t>
+          <t>76327</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -9409,17 +9464,17 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>OB_STG_BSOP3800</t>
+          <t>OB_STG_BSTR2213</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>E01</t>
+          <t>A65b</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>78851</t>
+          <t>76327</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -9436,17 +9491,17 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>OB_STG_BSOP3800</t>
+          <t>OB_STG_BSTR2213</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>A83</t>
+          <t>A10</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>78851</t>
+          <t>76327</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
@@ -9463,17 +9518,17 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>OB_STG_BSOP3800</t>
+          <t>OB_STG_BSEA2280</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>A82c</t>
+          <t>E06</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>78851</t>
+          <t>38611</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
@@ -9490,17 +9545,17 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>OB_STG_BSOP3800</t>
+          <t>OB_STG_BSEA2280</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>A42</t>
+          <t>E05</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>78851</t>
+          <t>38611</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -9517,17 +9572,17 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>OB_STG_BSOP3800</t>
+          <t>OB_STG_BSEA2280</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>A10</t>
+          <t>E01</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>78851</t>
+          <t>38611</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
@@ -9544,17 +9599,17 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>OB_STG_BAA9911</t>
+          <t>OB_STG_BSEA2280</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>A61</t>
+          <t>A92</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>76453</t>
+          <t>38611</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -9571,17 +9626,17 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>OB_STG_BSTR2213</t>
+          <t>OB_STG_BSEA2280</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>S66</t>
+          <t>A65b</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>76327</t>
+          <t>38611</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
@@ -9598,17 +9653,17 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>OB_STG_BSTR2213</t>
+          <t>OB_STG_BSEA2280</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>E06</t>
+          <t>A10</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>76327</t>
+          <t>38611</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
@@ -9625,17 +9680,17 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>OB_STG_BSTR2213</t>
+          <t>OB_STG_BSEA2280</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>E05</t>
+          <t>A07c</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>76327</t>
+          <t>38611</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
@@ -9652,17 +9707,17 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>OB_STG_BSTR2213</t>
+          <t>OB_STG_BSEA2810</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>A92</t>
+          <t>E11</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>76327</t>
+          <t>76311</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
@@ -9679,17 +9734,17 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>OB_STG_BSTR2213</t>
+          <t>OB_STG_BSEA2810</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>A67b</t>
+          <t>E06</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>76327</t>
+          <t>76311</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
@@ -9706,17 +9761,17 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>OB_STG_BSTR2213</t>
+          <t>OB_STG_BSEA2810</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>A65b</t>
+          <t>E05</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>76327</t>
+          <t>76311</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
@@ -9733,17 +9788,17 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>OB_STG_BSTR2213</t>
+          <t>OB_STG_BSEA2810</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>A10</t>
+          <t>E01</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>76327</t>
+          <t>76311</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
@@ -9760,17 +9815,17 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA2280</t>
+          <t>OB_STG_BSEA2810</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>E06</t>
+          <t>A65b</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>38611</t>
+          <t>76311</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
@@ -9787,17 +9842,17 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA2280</t>
+          <t>OB_STG_BSEA2810</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>E05</t>
+          <t>A07c</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>38611</t>
+          <t>76311</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
@@ -9814,17 +9869,17 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA2280</t>
+          <t>OB_STG_BSCS1010</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>E01</t>
+          <t>S59</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>38611</t>
+          <t>75373</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
@@ -9841,17 +9896,17 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA2280</t>
+          <t>OB_STG_BSCS1010</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>A92</t>
+          <t>E06</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>38611</t>
+          <t>75373</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
@@ -9868,17 +9923,17 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA2280</t>
+          <t>OB_STG_BSCS1010</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>A65b</t>
+          <t>E05</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>38611</t>
+          <t>75373</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
@@ -9895,17 +9950,17 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA2280</t>
+          <t>OB_STG_BSCS1010</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>A10</t>
+          <t>A92</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>38611</t>
+          <t>75373</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
@@ -9922,17 +9977,17 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA2280</t>
+          <t>OB_STG_BSCS1010</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>A07c</t>
+          <t>A65b</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>38611</t>
+          <t>75373</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
@@ -9949,17 +10004,17 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA2810</t>
+          <t>OB_STG_BSCS1010</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>E11</t>
+          <t>A26</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>76311</t>
+          <t>75373</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
@@ -9976,17 +10031,17 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA2810</t>
+          <t>OB_STG_BSCS1010</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>E06</t>
+          <t>A10</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>76311</t>
+          <t>75373</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
@@ -10003,17 +10058,17 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA2810</t>
+          <t>OB_STG_BSCP1500</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>E05</t>
+          <t>S47b</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>76311</t>
+          <t>33601</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
@@ -10030,17 +10085,17 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA2810</t>
+          <t>OB_STG_BSCP1500</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>E01</t>
+          <t>E13</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>76311</t>
+          <t>33601</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
@@ -10057,17 +10112,17 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA2810</t>
+          <t>OB_STG_BSCP1500</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>A65b</t>
+          <t>E05</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>76311</t>
+          <t>33601</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
@@ -10084,17 +10139,17 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA2810</t>
+          <t>OB_STG_BSCP1500</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>A07c</t>
+          <t>E01</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>76311</t>
+          <t>33601</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
@@ -10111,17 +10166,17 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS1010</t>
+          <t>OB_STG_BSCP1500</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>S59</t>
+          <t>A83</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>75373</t>
+          <t>33601</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
@@ -10138,17 +10193,17 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS1010</t>
+          <t>OB_STG_BSCP1500</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>E06</t>
+          <t>A82</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>75373</t>
+          <t>33601</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
@@ -10165,17 +10220,17 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS1010</t>
+          <t>OB_STG_BSCP1500</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>E05</t>
+          <t>A58b</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>75373</t>
+          <t>33601</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
@@ -10192,17 +10247,17 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS1010</t>
+          <t>OB_STG_BSCP1500</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>A92</t>
+          <t>A07</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>75373</t>
+          <t>33601</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
@@ -10219,17 +10274,17 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS1010</t>
+          <t>OB_STG_BSCP1407</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>A65b</t>
+          <t>S47b</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>75373</t>
+          <t>31294</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
@@ -10246,17 +10301,17 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS1010</t>
+          <t>OB_STG_BSCP1407</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>A26</t>
+          <t>E07b</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>75373</t>
+          <t>31294</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
@@ -10273,17 +10328,17 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS1010</t>
+          <t>OB_STG_BSCP1407</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>A10</t>
+          <t>E01</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>75373</t>
+          <t>31294</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
@@ -10300,17 +10355,17 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP1500</t>
+          <t>OB_STG_BSCP1407</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>S47b</t>
+          <t>A83b</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>33601</t>
+          <t>31294</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
@@ -10327,17 +10382,17 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP1500</t>
+          <t>OB_STG_BSCP1407</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>E13</t>
+          <t>A82</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>33601</t>
+          <t>31294</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
@@ -10354,17 +10409,17 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP1500</t>
+          <t>OB_STG_BSCP1407</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>E05</t>
+          <t>A32</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>33601</t>
+          <t>31294</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
@@ -10381,17 +10436,17 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP1500</t>
+          <t>OB_STG_BSCP1407</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>E01</t>
+          <t>A24</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>33601</t>
+          <t>31294</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
@@ -10408,17 +10463,17 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP1500</t>
+          <t>OB_STG_BSU9208</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>A83</t>
+          <t>S65</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>33601</t>
+          <t>78261</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
@@ -10435,17 +10490,17 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP1500</t>
+          <t>OB_STG_BSU9208</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>A82</t>
+          <t>S46</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>33601</t>
+          <t>78261</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
@@ -10462,17 +10517,17 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP1500</t>
+          <t>OB_STG_BSU9208</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>A58b</t>
+          <t>S45a</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>33601</t>
+          <t>78261</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
@@ -10489,17 +10544,17 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP1500</t>
+          <t>OB_STG_BSU9208</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>A07</t>
+          <t>S44</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>33601</t>
+          <t>78261</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
@@ -10516,17 +10571,17 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP1407</t>
+          <t>OB_STG_BSCS1405</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>S47b</t>
+          <t>S59</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>31294</t>
+          <t>34944</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
@@ -10543,17 +10598,17 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP1407</t>
+          <t>OB_STG_BSCS1405</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>E07b</t>
+          <t>E23</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>31294</t>
+          <t>34944</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
@@ -10570,17 +10625,17 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP1407</t>
+          <t>OB_STG_BSCS1405</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>E01</t>
+          <t>E03</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>31294</t>
+          <t>34944</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
@@ -10597,17 +10652,17 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP1407</t>
+          <t>OB_STG_BSCS1405</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>A83b</t>
+          <t>E01</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>31294</t>
+          <t>34944</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
@@ -10624,17 +10679,17 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP1407</t>
+          <t>OB_STG_BSCS1405</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>A82</t>
+          <t>A82c</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>31294</t>
+          <t>34944</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
@@ -10651,17 +10706,17 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP1407</t>
+          <t>OB_STG_BSCS1405</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>A32</t>
+          <t>A01</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>31294</t>
+          <t>34944</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
@@ -10678,17 +10733,17 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP1407</t>
+          <t>OB_STG_BSCS1403</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>A24</t>
+          <t>S59</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>31294</t>
+          <t>35167</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
@@ -10705,17 +10760,17 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>OB_STG_BSU9208</t>
+          <t>OB_STG_BSCS1403</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>S65</t>
+          <t>E17</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>78261</t>
+          <t>35167</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
@@ -10732,17 +10787,17 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>OB_STG_BSU9208</t>
+          <t>OB_STG_BSCS1403</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>S46</t>
+          <t>E05</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>78261</t>
+          <t>35167</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
@@ -10759,17 +10814,17 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>OB_STG_BSU9208</t>
+          <t>OB_STG_BSCS1403</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>S45a</t>
+          <t>E03</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>78261</t>
+          <t>35167</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
@@ -10786,17 +10841,17 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>OB_STG_BSU9208</t>
+          <t>OB_STG_BSCS1403</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>S44</t>
+          <t>E01</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>78261</t>
+          <t>35167</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
@@ -10813,17 +10868,17 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS1405</t>
+          <t>OB_STG_BSCS1403</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>S59</t>
+          <t>A94</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>34944</t>
+          <t>35167</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
@@ -10840,17 +10895,17 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS1405</t>
+          <t>OB_STG_BSCS1403</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>E23</t>
+          <t>A82</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>34944</t>
+          <t>35167</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
@@ -10867,17 +10922,17 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS1405</t>
+          <t>OB_STG_BSEA14081</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>E03</t>
+          <t>E10</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>34944</t>
+          <t>30648</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
@@ -10894,17 +10949,17 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS1405</t>
+          <t>OB_STG_BSEA14081</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>E01</t>
+          <t>E09</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>34944</t>
+          <t>30648</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
@@ -10921,17 +10976,17 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS1405</t>
+          <t>OB_STG_BSEA14081</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>A82c</t>
+          <t>E08</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>34944</t>
+          <t>30648</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
@@ -10948,17 +11003,17 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS1405</t>
+          <t>OB_STG_BSEA14081</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>A01</t>
+          <t>A23</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>34944</t>
+          <t>30648</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
@@ -10975,17 +11030,17 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS1403</t>
+          <t>OB_STG_BSMP3000</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>S59</t>
+          <t>E25</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>35167</t>
+          <t>75420</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
@@ -11002,17 +11057,17 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS1403</t>
+          <t>OB_STG_BSMP3000</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>E17</t>
+          <t>E05</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>35167</t>
+          <t>75420</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
@@ -11029,17 +11084,17 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS1403</t>
+          <t>OB_STG_BSMP3000</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>E05</t>
+          <t>E01</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>35167</t>
+          <t>75420</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
@@ -11056,17 +11111,17 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS1403</t>
+          <t>OB_STG_BSMP3000</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>E03</t>
+          <t>A83b</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>35167</t>
+          <t>75420</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
@@ -11083,17 +11138,17 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS1403</t>
+          <t>OB_STG_BSMP3000</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>E01</t>
+          <t>A13b</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>35167</t>
+          <t>75420</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
@@ -11110,17 +11165,17 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS1403</t>
+          <t>OB_STG_BSMP3000</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>A94</t>
+          <t>A10</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>35167</t>
+          <t>75420</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
@@ -11137,17 +11192,17 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS1403</t>
+          <t>OB_STG_BSMP3000</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>A82</t>
+          <t>A07</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>35167</t>
+          <t>75420</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
@@ -11164,17 +11219,17 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA14081</t>
+          <t>OB_STG_BSMP3700</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>E10</t>
+          <t>S49</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>30648</t>
+          <t>31101</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
@@ -11191,17 +11246,17 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA14081</t>
+          <t>OB_STG_BSMP3700</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>E09</t>
+          <t>E05</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>30648</t>
+          <t>31101</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
@@ -11218,17 +11273,17 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA14081</t>
+          <t>OB_STG_BSMP3700</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>E08</t>
+          <t>A88</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>30648</t>
+          <t>31101</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
@@ -11245,17 +11300,17 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA14081</t>
+          <t>OB_STG_BSMP3700</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>A23</t>
+          <t>A87</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>30648</t>
+          <t>31101</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
@@ -11272,17 +11327,17 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP3000</t>
+          <t>OB_STG_BSMP3700</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>E25</t>
+          <t>A82b</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>75420</t>
+          <t>31101</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
@@ -11299,17 +11354,17 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP3000</t>
+          <t>OB_STG_BSMP3700</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>E05</t>
+          <t>A79</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>75420</t>
+          <t>31101</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
@@ -11326,17 +11381,17 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP3000</t>
+          <t>OB_STG_BSMP3700</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>E01</t>
+          <t>A07b</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>75420</t>
+          <t>31101</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
@@ -11353,17 +11408,17 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP3000</t>
+          <t>OB_STG_BSMP1401</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>A83b</t>
+          <t>E05</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>75420</t>
+          <t>34809</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
@@ -11380,17 +11435,17 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP3000</t>
+          <t>OB_STG_BSMP1401</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>A13b</t>
+          <t>E01</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>75420</t>
+          <t>34809</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
@@ -11407,17 +11462,17 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP3000</t>
+          <t>OB_STG_BSMP1401</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>A10</t>
+          <t>A75</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>75420</t>
+          <t>34809</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
@@ -11434,17 +11489,17 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP3000</t>
+          <t>OB_STG_BSMP1401</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>A07</t>
+          <t>A10</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>75420</t>
+          <t>34809</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
@@ -11461,17 +11516,17 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP3700</t>
+          <t>OB_STG_BSMP1401</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>S49</t>
+          <t>A07c</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>31101</t>
+          <t>34809</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
@@ -11488,17 +11543,17 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP3700</t>
+          <t>OB_STG_BSTA1003</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>E05</t>
+          <t>S26b</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>31101</t>
+          <t>35716</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
@@ -11515,17 +11570,17 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP3700</t>
+          <t>OB_STG_BSTA1003</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>A88</t>
+          <t>S21</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>31101</t>
+          <t>35716</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
@@ -11542,17 +11597,17 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP3700</t>
+          <t>OB_STG_BSTA1003</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>A87</t>
+          <t>E01</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>31101</t>
+          <t>35716</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
@@ -11569,17 +11624,17 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP3700</t>
+          <t>OB_STG_BSTA1003</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>A82b</t>
+          <t>A35</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>31101</t>
+          <t>35716</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
@@ -11596,17 +11651,17 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP3700</t>
+          <t>OB_STG_BSTA1002</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>A79</t>
+          <t>A51</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>31101</t>
+          <t>75578</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
@@ -11623,17 +11678,17 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP3700</t>
+          <t>OB_STG_BSTA1002</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>A07b</t>
+          <t>S24</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>31101</t>
+          <t>75578</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
@@ -11650,17 +11705,17 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP1401</t>
+          <t>OB_STG_BSTA1002</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>E05</t>
+          <t>S23</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>34809</t>
+          <t>75578</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
@@ -11677,17 +11732,17 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP1401</t>
+          <t>OB_STG_BSTA1002</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>E01</t>
+          <t>S22</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>34809</t>
+          <t>75578</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
@@ -11704,17 +11759,17 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP1401</t>
+          <t>OB_STG_BSTA1002</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>A75</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>34809</t>
+          <t>75578</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
@@ -11731,17 +11786,17 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP1401</t>
+          <t>OB_STG_BSCP1404</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>A10</t>
+          <t>E07e</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>34809</t>
+          <t>70555</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
@@ -11758,17 +11813,17 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP1401</t>
+          <t>OB_STG_BSCP1404</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>A07c</t>
+          <t>E01</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>34809</t>
+          <t>70555</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
@@ -11785,17 +11840,17 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>OB_STG_BSTA1003</t>
+          <t>OB_STG_BSCP1404</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>S26b</t>
+          <t>A83c</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>35716</t>
+          <t>70555</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
@@ -11812,17 +11867,17 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>OB_STG_BSTA1003</t>
+          <t>OB_STG_BSCP1404</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>S21</t>
+          <t>A83b</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>35716</t>
+          <t>70555</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
@@ -11839,17 +11894,17 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>OB_STG_BSTA1003</t>
+          <t>OB_STG_BSCP1404</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>E01</t>
+          <t>A74</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>35716</t>
+          <t>70555</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
@@ -11866,17 +11921,17 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>OB_STG_BSTA1003</t>
+          <t>OB_STG_BSOP1901</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>A35</t>
+          <t>S56</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>35716</t>
+          <t>71845</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
@@ -11893,17 +11948,17 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>OB_STG_BSTA1002</t>
+          <t>OB_STG_BSOP1901</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>A51</t>
+          <t>E01</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>75578</t>
+          <t>71845</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
@@ -11920,17 +11975,17 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>OB_STG_BSTA1002</t>
+          <t>OB_STG_BSOP1901</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>S24</t>
+          <t>A95</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>75578</t>
+          <t>71845</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
@@ -11947,17 +12002,17 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>OB_STG_BSTA1002</t>
+          <t>OB_STG_BSOP1901</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>S23</t>
+          <t>A51</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>75578</t>
+          <t>71845</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
@@ -11974,17 +12029,17 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>OB_STG_BSTA1002</t>
+          <t>OB_STG_BSOP1901</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>S22</t>
+          <t>A10b</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>75578</t>
+          <t>71845</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
@@ -12001,17 +12056,17 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>OB_STG_BSTA1002</t>
+          <t>OB_STG_BSU1405</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>S16</t>
+          <t>S47</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>75578</t>
+          <t>72328</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
@@ -12028,12 +12083,17 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>OB_STG_BSOP4000</t>
+          <t>OB_STG_BSU1405</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>E01</t>
+          <t>S42</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>72328</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
@@ -12050,12 +12110,17 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>OB_STG_BSOP4000</t>
+          <t>OB_STG_BSU1405</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>A71</t>
+          <t>E26</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>72328</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
@@ -12072,17 +12137,17 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP1404</t>
+          <t>OB_STG_BSOP2214</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>E07e</t>
+          <t>E01</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>70555</t>
+          <t>78857</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
@@ -12099,17 +12164,17 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP1404</t>
+          <t>OB_STG_BSOP2214</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>E01</t>
+          <t>A64</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>70555</t>
+          <t>78857</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
@@ -12126,17 +12191,17 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP1404</t>
+          <t>OB_STG_BSOP2214</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>A83c</t>
+          <t>A60</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>70555</t>
+          <t>78857</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
@@ -12153,17 +12218,17 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP1404</t>
+          <t>OB_STG_BSOP2214</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>A83b</t>
+          <t>A59</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>70555</t>
+          <t>78857</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
@@ -12180,17 +12245,17 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP1404</t>
+          <t>OB_STG_BSOP2214</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>A74</t>
+          <t>A10c</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>70555</t>
+          <t>78857</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
@@ -12207,17 +12272,17 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>OB_STG_BSOP1901</t>
+          <t>OB_STG_BSCS1404</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>S56</t>
+          <t>S59</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>71845</t>
+          <t>72329</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
@@ -12234,17 +12299,17 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>OB_STG_BSOP1901</t>
+          <t>OB_STG_BSCS1404</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>E01</t>
+          <t>S52</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>71845</t>
+          <t>72329</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
@@ -12261,17 +12326,17 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>OB_STG_BSOP1901</t>
+          <t>OB_STG_BSCS1404</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>A95</t>
+          <t>E07</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>71845</t>
+          <t>72329</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
@@ -12288,17 +12353,17 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>OB_STG_BSOP1901</t>
+          <t>OB_STG_BSCS1404</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>A51</t>
+          <t>E01</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>71845</t>
+          <t>72329</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
@@ -12315,17 +12380,17 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>OB_STG_BSOP1901</t>
+          <t>OB_STG_BSCS1404</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>A10b</t>
+          <t>A82b</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>71845</t>
+          <t>72329</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
@@ -12342,17 +12407,17 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>OB_STG_BSU1405</t>
+          <t>OB_STG_BSCS1404</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>S47</t>
+          <t>A34</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>72328</t>
+          <t>72329</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
@@ -12369,17 +12434,17 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>OB_STG_BSU1405</t>
+          <t>OB_STG_BSCS1404</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>S42</t>
+          <t>A20</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>72328</t>
+          <t>72329</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
@@ -12396,17 +12461,17 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>OB_STG_BSU1405</t>
+          <t>OB_STG_BSCS1404</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>E26</t>
+          <t>A01</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>72328</t>
+          <t>72329</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
@@ -12415,445 +12480,6 @@
         </is>
       </c>
       <c r="E447" t="inlineStr">
-        <is>
-          <t>31/12/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="448">
-      <c r="A448" t="inlineStr">
-        <is>
-          <t>OB_STG_BSOP2214</t>
-        </is>
-      </c>
-      <c r="B448" t="inlineStr">
-        <is>
-          <t>E01</t>
-        </is>
-      </c>
-      <c r="C448" t="inlineStr">
-        <is>
-          <t>78857</t>
-        </is>
-      </c>
-      <c r="D448" t="inlineStr">
-        <is>
-          <t>01/01/2026</t>
-        </is>
-      </c>
-      <c r="E448" t="inlineStr">
-        <is>
-          <t>31/12/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="449">
-      <c r="A449" t="inlineStr">
-        <is>
-          <t>OB_STG_BSOP2214</t>
-        </is>
-      </c>
-      <c r="B449" t="inlineStr">
-        <is>
-          <t>A64</t>
-        </is>
-      </c>
-      <c r="C449" t="inlineStr">
-        <is>
-          <t>78857</t>
-        </is>
-      </c>
-      <c r="D449" t="inlineStr">
-        <is>
-          <t>01/01/2026</t>
-        </is>
-      </c>
-      <c r="E449" t="inlineStr">
-        <is>
-          <t>31/12/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="450">
-      <c r="A450" t="inlineStr">
-        <is>
-          <t>OB_STG_BSOP2214</t>
-        </is>
-      </c>
-      <c r="B450" t="inlineStr">
-        <is>
-          <t>A60</t>
-        </is>
-      </c>
-      <c r="C450" t="inlineStr">
-        <is>
-          <t>78857</t>
-        </is>
-      </c>
-      <c r="D450" t="inlineStr">
-        <is>
-          <t>01/01/2026</t>
-        </is>
-      </c>
-      <c r="E450" t="inlineStr">
-        <is>
-          <t>31/12/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="451">
-      <c r="A451" t="inlineStr">
-        <is>
-          <t>OB_STG_BSOP2214</t>
-        </is>
-      </c>
-      <c r="B451" t="inlineStr">
-        <is>
-          <t>A59</t>
-        </is>
-      </c>
-      <c r="C451" t="inlineStr">
-        <is>
-          <t>78857</t>
-        </is>
-      </c>
-      <c r="D451" t="inlineStr">
-        <is>
-          <t>01/01/2026</t>
-        </is>
-      </c>
-      <c r="E451" t="inlineStr">
-        <is>
-          <t>31/12/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="452">
-      <c r="A452" t="inlineStr">
-        <is>
-          <t>OB_STG_BSOP2214</t>
-        </is>
-      </c>
-      <c r="B452" t="inlineStr">
-        <is>
-          <t>A10c</t>
-        </is>
-      </c>
-      <c r="C452" t="inlineStr">
-        <is>
-          <t>78857</t>
-        </is>
-      </c>
-      <c r="D452" t="inlineStr">
-        <is>
-          <t>01/01/2026</t>
-        </is>
-      </c>
-      <c r="E452" t="inlineStr">
-        <is>
-          <t>31/12/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="453">
-      <c r="A453" t="inlineStr">
-        <is>
-          <t>OB_STG_BSEA1410</t>
-        </is>
-      </c>
-      <c r="B453" t="inlineStr">
-        <is>
-          <t>A82</t>
-        </is>
-      </c>
-      <c r="D453" t="inlineStr">
-        <is>
-          <t>01/01/2026</t>
-        </is>
-      </c>
-      <c r="E453" t="inlineStr">
-        <is>
-          <t>31/12/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="454">
-      <c r="A454" t="inlineStr">
-        <is>
-          <t>OB_STG_BSEA1410</t>
-        </is>
-      </c>
-      <c r="B454" t="inlineStr">
-        <is>
-          <t>A44</t>
-        </is>
-      </c>
-      <c r="D454" t="inlineStr">
-        <is>
-          <t>01/01/2026</t>
-        </is>
-      </c>
-      <c r="E454" t="inlineStr">
-        <is>
-          <t>31/12/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="455">
-      <c r="A455" t="inlineStr">
-        <is>
-          <t>OB_STG_BSEA1410</t>
-        </is>
-      </c>
-      <c r="B455" t="inlineStr">
-        <is>
-          <t>A39</t>
-        </is>
-      </c>
-      <c r="D455" t="inlineStr">
-        <is>
-          <t>01/01/2026</t>
-        </is>
-      </c>
-      <c r="E455" t="inlineStr">
-        <is>
-          <t>31/12/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="456">
-      <c r="A456" t="inlineStr">
-        <is>
-          <t>OB_STG_BSEA1410</t>
-        </is>
-      </c>
-      <c r="B456" t="inlineStr">
-        <is>
-          <t>A07c</t>
-        </is>
-      </c>
-      <c r="D456" t="inlineStr">
-        <is>
-          <t>01/01/2026</t>
-        </is>
-      </c>
-      <c r="E456" t="inlineStr">
-        <is>
-          <t>31/12/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="457">
-      <c r="A457" t="inlineStr">
-        <is>
-          <t>OB_STG_BSCS1404</t>
-        </is>
-      </c>
-      <c r="B457" t="inlineStr">
-        <is>
-          <t>S59</t>
-        </is>
-      </c>
-      <c r="C457" t="inlineStr">
-        <is>
-          <t>72329</t>
-        </is>
-      </c>
-      <c r="D457" t="inlineStr">
-        <is>
-          <t>01/01/2026</t>
-        </is>
-      </c>
-      <c r="E457" t="inlineStr">
-        <is>
-          <t>31/12/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="458">
-      <c r="A458" t="inlineStr">
-        <is>
-          <t>OB_STG_BSCS1404</t>
-        </is>
-      </c>
-      <c r="B458" t="inlineStr">
-        <is>
-          <t>S52</t>
-        </is>
-      </c>
-      <c r="C458" t="inlineStr">
-        <is>
-          <t>72329</t>
-        </is>
-      </c>
-      <c r="D458" t="inlineStr">
-        <is>
-          <t>01/01/2026</t>
-        </is>
-      </c>
-      <c r="E458" t="inlineStr">
-        <is>
-          <t>31/12/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="459">
-      <c r="A459" t="inlineStr">
-        <is>
-          <t>OB_STG_BSCS1404</t>
-        </is>
-      </c>
-      <c r="B459" t="inlineStr">
-        <is>
-          <t>E07</t>
-        </is>
-      </c>
-      <c r="C459" t="inlineStr">
-        <is>
-          <t>72329</t>
-        </is>
-      </c>
-      <c r="D459" t="inlineStr">
-        <is>
-          <t>01/01/2026</t>
-        </is>
-      </c>
-      <c r="E459" t="inlineStr">
-        <is>
-          <t>31/12/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="460">
-      <c r="A460" t="inlineStr">
-        <is>
-          <t>OB_STG_BSCS1404</t>
-        </is>
-      </c>
-      <c r="B460" t="inlineStr">
-        <is>
-          <t>E01</t>
-        </is>
-      </c>
-      <c r="C460" t="inlineStr">
-        <is>
-          <t>72329</t>
-        </is>
-      </c>
-      <c r="D460" t="inlineStr">
-        <is>
-          <t>01/01/2026</t>
-        </is>
-      </c>
-      <c r="E460" t="inlineStr">
-        <is>
-          <t>31/12/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="461">
-      <c r="A461" t="inlineStr">
-        <is>
-          <t>OB_STG_BSCS1404</t>
-        </is>
-      </c>
-      <c r="B461" t="inlineStr">
-        <is>
-          <t>A82b</t>
-        </is>
-      </c>
-      <c r="C461" t="inlineStr">
-        <is>
-          <t>72329</t>
-        </is>
-      </c>
-      <c r="D461" t="inlineStr">
-        <is>
-          <t>01/01/2026</t>
-        </is>
-      </c>
-      <c r="E461" t="inlineStr">
-        <is>
-          <t>31/12/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="462">
-      <c r="A462" t="inlineStr">
-        <is>
-          <t>OB_STG_BSCS1404</t>
-        </is>
-      </c>
-      <c r="B462" t="inlineStr">
-        <is>
-          <t>A34</t>
-        </is>
-      </c>
-      <c r="C462" t="inlineStr">
-        <is>
-          <t>72329</t>
-        </is>
-      </c>
-      <c r="D462" t="inlineStr">
-        <is>
-          <t>01/01/2026</t>
-        </is>
-      </c>
-      <c r="E462" t="inlineStr">
-        <is>
-          <t>31/12/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="463">
-      <c r="A463" t="inlineStr">
-        <is>
-          <t>OB_STG_BSCS1404</t>
-        </is>
-      </c>
-      <c r="B463" t="inlineStr">
-        <is>
-          <t>A20</t>
-        </is>
-      </c>
-      <c r="C463" t="inlineStr">
-        <is>
-          <t>72329</t>
-        </is>
-      </c>
-      <c r="D463" t="inlineStr">
-        <is>
-          <t>01/01/2026</t>
-        </is>
-      </c>
-      <c r="E463" t="inlineStr">
-        <is>
-          <t>31/12/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="464">
-      <c r="A464" t="inlineStr">
-        <is>
-          <t>OB_STG_BSCS1404</t>
-        </is>
-      </c>
-      <c r="B464" t="inlineStr">
-        <is>
-          <t>A01</t>
-        </is>
-      </c>
-      <c r="C464" t="inlineStr">
-        <is>
-          <t>72329</t>
-        </is>
-      </c>
-      <c r="D464" t="inlineStr">
-        <is>
-          <t>01/01/2026</t>
-        </is>
-      </c>
-      <c r="E464" t="inlineStr">
         <is>
           <t>31/12/2026</t>
         </is>

--- a/script/templates/WePartyInterface_BS.xlsx
+++ b/script/templates/WePartyInterface_BS.xlsx
@@ -446,7 +446,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>OB_PF_STG_BSA9090</t>
+          <t>2026_OB_PF_STG_BSA9090</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -473,7 +473,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>OB_STG_BAA9001</t>
+          <t>2026_OB_STG_BAA9001</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -500,7 +500,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>OB_STG_BSTA4600</t>
+          <t>2026_OB_STG_BSTA4600</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -527,7 +527,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>OB_STG_BSTA4600</t>
+          <t>2026_OB_STG_BSTA4600</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -554,7 +554,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>OB_STG_BSTA4600</t>
+          <t>2026_OB_STG_BSTA4600</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -581,7 +581,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>OB_STG_BSTA4600</t>
+          <t>2026_OB_STG_BSTA4600</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -608,7 +608,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>OB_STG_BSTA4600</t>
+          <t>2026_OB_STG_BSTA4600</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -635,7 +635,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>OB_STG_BSTA4600</t>
+          <t>2026_OB_STG_BSTA4600</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -662,7 +662,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>OB_STG_BSU7200</t>
+          <t>2026_OB_STG_BSU7200</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -689,7 +689,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>OB_STG_BSU7200</t>
+          <t>2026_OB_STG_BSU7200</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -716,7 +716,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>OB_STG_BSU7200</t>
+          <t>2026_OB_STG_BSU7200</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -743,7 +743,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>OB_STG_BSU7200</t>
+          <t>2026_OB_STG_BSU7200</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -770,7 +770,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>OB_STG_BSU7200</t>
+          <t>2026_OB_STG_BSU7200</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -797,7 +797,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>OB_STG_BSU7200</t>
+          <t>2026_OB_STG_BSU7200</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -824,7 +824,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP2000</t>
+          <t>2026_OB_STG_BSMP2000</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -851,7 +851,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP2000</t>
+          <t>2026_OB_STG_BSMP2000</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -878,7 +878,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP2000</t>
+          <t>2026_OB_STG_BSMP2000</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -905,7 +905,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP2000</t>
+          <t>2026_OB_STG_BSMP2000</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -932,7 +932,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP2000</t>
+          <t>2026_OB_STG_BSMP2000</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -959,7 +959,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP2000</t>
+          <t>2026_OB_STG_BSMP2000</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -986,7 +986,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP2000</t>
+          <t>2026_OB_STG_BSMP2000</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1013,7 +1013,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA4820</t>
+          <t>2026_OB_STG_BSEA4820</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1040,7 +1040,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA4820</t>
+          <t>2026_OB_STG_BSEA4820</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1067,7 +1067,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA4820</t>
+          <t>2026_OB_STG_BSEA4820</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1094,7 +1094,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA4820</t>
+          <t>2026_OB_STG_BSEA4820</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1121,7 +1121,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA4820</t>
+          <t>2026_OB_STG_BSEA4820</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1148,7 +1148,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA4820</t>
+          <t>2026_OB_STG_BSEA4820</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1175,7 +1175,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA4820</t>
+          <t>2026_OB_STG_BSEA4820</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1202,7 +1202,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA4820</t>
+          <t>2026_OB_STG_BSEA4820</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1229,7 +1229,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA0120</t>
+          <t>2026_OB_STG_BSEA0120</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1256,7 +1256,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA0120</t>
+          <t>2026_OB_STG_BSEA0120</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1283,7 +1283,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA0120</t>
+          <t>2026_OB_STG_BSEA0120</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1310,7 +1310,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA0120</t>
+          <t>2026_OB_STG_BSEA0120</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1337,7 +1337,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA0120</t>
+          <t>2026_OB_STG_BSEA0120</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1364,7 +1364,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA0120</t>
+          <t>2026_OB_STG_BSEA0120</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1391,7 +1391,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA0120</t>
+          <t>2026_OB_STG_BSEA0120</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1418,7 +1418,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA2200</t>
+          <t>2026_OB_STG_BSEA2200</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1445,7 +1445,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA2200</t>
+          <t>2026_OB_STG_BSEA2200</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1472,7 +1472,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA2200</t>
+          <t>2026_OB_STG_BSEA2200</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA2200</t>
+          <t>2026_OB_STG_BSEA2200</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1526,7 +1526,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA2200</t>
+          <t>2026_OB_STG_BSEA2200</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1553,7 +1553,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>OB_STG_BSTR0902</t>
+          <t>2026_OB_STG_BSTR0902</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1580,7 +1580,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>OB_STG_BSTR0902</t>
+          <t>2026_OB_STG_BSTR0902</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1607,7 +1607,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>OB_STG_BSTR0902</t>
+          <t>2026_OB_STG_BSTR0902</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1634,7 +1634,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>OB_STG_BSTR0902</t>
+          <t>2026_OB_STG_BSTR0902</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1661,7 +1661,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>OB_STG_BSTR0902</t>
+          <t>2026_OB_STG_BSTR0902</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1688,7 +1688,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>OB_STG_BSTR0902</t>
+          <t>2026_OB_STG_BSTR0902</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1715,7 +1715,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>OB_STG_BSTR0902</t>
+          <t>2026_OB_STG_BSTR0902</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1742,7 +1742,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS0710</t>
+          <t>2026_OB_STG_BSCS0710</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1769,7 +1769,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS0710</t>
+          <t>2026_OB_STG_BSCS0710</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1796,7 +1796,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS0710</t>
+          <t>2026_OB_STG_BSCS0710</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1823,7 +1823,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS0710</t>
+          <t>2026_OB_STG_BSCS0710</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1850,7 +1850,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS0710</t>
+          <t>2026_OB_STG_BSCS0710</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1877,7 +1877,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS0710</t>
+          <t>2026_OB_STG_BSCS0710</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1904,7 +1904,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS0710</t>
+          <t>2026_OB_STG_BSCS0710</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1931,7 +1931,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS0710</t>
+          <t>2026_OB_STG_BSCS0710</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1958,7 +1958,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS0710</t>
+          <t>2026_OB_STG_BSCS0710</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1985,7 +1985,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS1600</t>
+          <t>2026_OB_STG_BSCS1600</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2012,7 +2012,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS1600</t>
+          <t>2026_OB_STG_BSCS1600</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2039,7 +2039,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS1600</t>
+          <t>2026_OB_STG_BSCS1600</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2066,7 +2066,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS1600</t>
+          <t>2026_OB_STG_BSCS1600</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2093,7 +2093,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS1600</t>
+          <t>2026_OB_STG_BSCS1600</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2120,7 +2120,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS1600</t>
+          <t>2026_OB_STG_BSCS1600</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2147,7 +2147,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS1600</t>
+          <t>2026_OB_STG_BSCS1600</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2174,7 +2174,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS1600</t>
+          <t>2026_OB_STG_BSCS1600</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS0600</t>
+          <t>2026_OB_STG_BSCS0600</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2228,7 +2228,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS0600</t>
+          <t>2026_OB_STG_BSCS0600</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2255,7 +2255,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS0600</t>
+          <t>2026_OB_STG_BSCS0600</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2282,7 +2282,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS0600</t>
+          <t>2026_OB_STG_BSCS0600</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2309,7 +2309,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS0600</t>
+          <t>2026_OB_STG_BSCS0600</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2336,7 +2336,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS0600</t>
+          <t>2026_OB_STG_BSCS0600</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2363,7 +2363,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS0600</t>
+          <t>2026_OB_STG_BSCS0600</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2390,7 +2390,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS0600</t>
+          <t>2026_OB_STG_BSCS0600</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2417,7 +2417,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS2230</t>
+          <t>2026_OB_STG_BSCS2230</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2444,7 +2444,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS2230</t>
+          <t>2026_OB_STG_BSCS2230</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2471,7 +2471,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS2230</t>
+          <t>2026_OB_STG_BSCS2230</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2498,7 +2498,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS2230</t>
+          <t>2026_OB_STG_BSCS2230</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2525,7 +2525,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS2230</t>
+          <t>2026_OB_STG_BSCS2230</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2552,7 +2552,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS2230</t>
+          <t>2026_OB_STG_BSCS2230</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2579,7 +2579,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS2230</t>
+          <t>2026_OB_STG_BSCS2230</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2606,7 +2606,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS1402</t>
+          <t>2026_OB_STG_BSCS1402</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2633,7 +2633,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS1402</t>
+          <t>2026_OB_STG_BSCS1402</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2660,7 +2660,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS1402</t>
+          <t>2026_OB_STG_BSCS1402</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2687,7 +2687,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS1402</t>
+          <t>2026_OB_STG_BSCS1402</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2714,7 +2714,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS1402</t>
+          <t>2026_OB_STG_BSCS1402</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2741,7 +2741,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS1402</t>
+          <t>2026_OB_STG_BSCS1402</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2768,7 +2768,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS1402</t>
+          <t>2026_OB_STG_BSCS1402</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2795,7 +2795,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS1402</t>
+          <t>2026_OB_STG_BSCS1402</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2822,7 +2822,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS3400</t>
+          <t>2026_OB_STG_BSCS3400</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2849,7 +2849,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS3400</t>
+          <t>2026_OB_STG_BSCS3400</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2876,7 +2876,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS3400</t>
+          <t>2026_OB_STG_BSCS3400</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2903,7 +2903,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS3400</t>
+          <t>2026_OB_STG_BSCS3400</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2930,7 +2930,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS3400</t>
+          <t>2026_OB_STG_BSCS3400</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2957,7 +2957,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS3400</t>
+          <t>2026_OB_STG_BSCS3400</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2984,7 +2984,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS3400</t>
+          <t>2026_OB_STG_BSCS3400</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3011,7 +3011,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS0903</t>
+          <t>2026_OB_STG_BSCS0903</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3038,7 +3038,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS0903</t>
+          <t>2026_OB_STG_BSCS0903</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3065,7 +3065,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS0903</t>
+          <t>2026_OB_STG_BSCS0903</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3092,7 +3092,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS0903</t>
+          <t>2026_OB_STG_BSCS0903</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3119,7 +3119,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS0903</t>
+          <t>2026_OB_STG_BSCS0903</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3146,7 +3146,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS0903</t>
+          <t>2026_OB_STG_BSCS0903</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3173,7 +3173,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS0903</t>
+          <t>2026_OB_STG_BSCS0903</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3200,7 +3200,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS0903</t>
+          <t>2026_OB_STG_BSCS0903</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3227,7 +3227,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>OB_STG_BAA9912</t>
+          <t>2026_OB_STG_BAA9912</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3254,7 +3254,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>OB_STG_BSOP1900</t>
+          <t>2026_OB_STG_BSOP1900</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -3281,7 +3281,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>OB_STG_BSOP1900</t>
+          <t>2026_OB_STG_BSOP1900</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3308,7 +3308,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>OB_STG_BSOP1900</t>
+          <t>2026_OB_STG_BSOP1900</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3335,7 +3335,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>OB_STG_BSOP1900</t>
+          <t>2026_OB_STG_BSOP1900</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3362,7 +3362,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>OB_STG_BSOP1900</t>
+          <t>2026_OB_STG_BSOP1900</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3389,7 +3389,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>OB_STG_BSOP1900</t>
+          <t>2026_OB_STG_BSOP1900</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -3416,7 +3416,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>OB_STG_BSOP1900</t>
+          <t>2026_OB_STG_BSOP1900</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3443,7 +3443,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>OB_STG_BSOP1911</t>
+          <t>2026_OB_STG_BSOP1911</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3470,7 +3470,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>OB_STG_BSOP1911</t>
+          <t>2026_OB_STG_BSOP1911</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3497,7 +3497,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>OB_STG_BSOP1911</t>
+          <t>2026_OB_STG_BSOP1911</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3524,7 +3524,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>OB_STG_BSOP1911</t>
+          <t>2026_OB_STG_BSOP1911</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3551,7 +3551,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>OB_STG_BSOP1911</t>
+          <t>2026_OB_STG_BSOP1911</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -3578,7 +3578,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>OB_STG_BSOP1911</t>
+          <t>2026_OB_STG_BSOP1911</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3605,7 +3605,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP1200</t>
+          <t>2026_OB_STG_BSMP1200</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3632,7 +3632,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP1200</t>
+          <t>2026_OB_STG_BSMP1200</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -3659,7 +3659,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP1200</t>
+          <t>2026_OB_STG_BSMP1200</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3686,7 +3686,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP1200</t>
+          <t>2026_OB_STG_BSMP1200</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3713,7 +3713,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP1200</t>
+          <t>2026_OB_STG_BSMP1200</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3740,7 +3740,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP1200</t>
+          <t>2026_OB_STG_BSMP1200</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3767,7 +3767,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP1200</t>
+          <t>2026_OB_STG_BSMP1200</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3794,7 +3794,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>OB_STG_BSTR0811</t>
+          <t>2026_OB_STG_BSTR0811</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -3821,7 +3821,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>OB_STG_BSTR0811</t>
+          <t>2026_OB_STG_BSTR0811</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -3848,7 +3848,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>OB_STG_BSTR0811</t>
+          <t>2026_OB_STG_BSTR0811</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3875,7 +3875,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>OB_STG_BSTR0811</t>
+          <t>2026_OB_STG_BSTR0811</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -3902,7 +3902,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>OB_STG_BSTR0811</t>
+          <t>2026_OB_STG_BSTR0811</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3929,7 +3929,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>OB_STG_BSTR0811</t>
+          <t>2026_OB_STG_BSTR0811</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3956,7 +3956,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>OB_PF_STG_BSTA4800</t>
+          <t>2026_OB_PF_STG_BSTA4800</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3983,7 +3983,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>OB_PF_STG_BSTA4800</t>
+          <t>2026_OB_PF_STG_BSTA4800</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -4010,7 +4010,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>OB_PF_STG_BSTA4800</t>
+          <t>2026_OB_PF_STG_BSTA4800</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -4037,7 +4037,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>OB_PF_STG_BSTA4800</t>
+          <t>2026_OB_PF_STG_BSTA4800</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -4064,7 +4064,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>OB_PF_STG_BSTA4800</t>
+          <t>2026_OB_PF_STG_BSTA4800</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -4091,7 +4091,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>OB_PF_STG_BSTA4800</t>
+          <t>2026_OB_PF_STG_BSTA4800</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -4118,7 +4118,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>OB_PF_STG_BSTA4800</t>
+          <t>2026_OB_PF_STG_BSTA4800</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -4145,7 +4145,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>OB_STG_BSTR2010</t>
+          <t>2026_OB_STG_BSTR2010</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -4172,7 +4172,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>OB_STG_BSTR2010</t>
+          <t>2026_OB_STG_BSTR2010</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -4199,7 +4199,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>OB_STG_BSTR2010</t>
+          <t>2026_OB_STG_BSTR2010</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -4226,7 +4226,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>OB_STG_BSTR2010</t>
+          <t>2026_OB_STG_BSTR2010</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -4253,7 +4253,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>OB_STG_BSTR2010</t>
+          <t>2026_OB_STG_BSTR2010</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -4280,7 +4280,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>OB_STG_BSTR2010</t>
+          <t>2026_OB_STG_BSTR2010</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -4307,7 +4307,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>OB_STG_BSTA4810</t>
+          <t>2026_OB_STG_BSTA4810</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -4334,7 +4334,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>OB_STG_BSTA4810</t>
+          <t>2026_OB_STG_BSTA4810</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -4361,7 +4361,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>OB_STG_BSTA4810</t>
+          <t>2026_OB_STG_BSTA4810</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -4388,7 +4388,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>OB_STG_BSTA4810</t>
+          <t>2026_OB_STG_BSTA4810</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -4415,7 +4415,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>OB_STG_BSTA4810</t>
+          <t>2026_OB_STG_BSTA4810</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -4442,7 +4442,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>OB_STG_BAA9905</t>
+          <t>2026_OB_STG_BAA9905</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -4469,7 +4469,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>OB_STG_BAA9905</t>
+          <t>2026_OB_STG_BAA9905</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -4496,7 +4496,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>OB_STG_BAA9903</t>
+          <t>2026_OB_STG_BAA9903</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -4523,7 +4523,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>OB_STG_BAA9903</t>
+          <t>2026_OB_STG_BAA9903</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -4550,7 +4550,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>OB_STG_BSU1409</t>
+          <t>2026_OB_STG_BSU1409</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -4577,7 +4577,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>OB_STG_BSU1409</t>
+          <t>2026_OB_STG_BSU1409</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -4604,7 +4604,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP1320</t>
+          <t>2026_OB_STG_BSMP1320</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -4631,7 +4631,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP1320</t>
+          <t>2026_OB_STG_BSMP1320</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -4658,7 +4658,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP1320</t>
+          <t>2026_OB_STG_BSMP1320</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -4685,7 +4685,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP1320</t>
+          <t>2026_OB_STG_BSMP1320</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -4712,7 +4712,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP1320</t>
+          <t>2026_OB_STG_BSMP1320</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -4739,7 +4739,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP1320</t>
+          <t>2026_OB_STG_BSMP1320</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -4766,7 +4766,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA1000</t>
+          <t>2026_OB_STG_BSEA1000</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -4793,7 +4793,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA1000</t>
+          <t>2026_OB_STG_BSEA1000</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -4820,7 +4820,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA1000</t>
+          <t>2026_OB_STG_BSEA1000</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -4847,7 +4847,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA1000</t>
+          <t>2026_OB_STG_BSEA1000</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -4874,7 +4874,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA1000</t>
+          <t>2026_OB_STG_BSEA1000</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -4901,7 +4901,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP1100</t>
+          <t>2026_OB_STG_BSMP1100</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -4928,7 +4928,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP1100</t>
+          <t>2026_OB_STG_BSMP1100</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -4955,7 +4955,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP1100</t>
+          <t>2026_OB_STG_BSMP1100</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -4982,7 +4982,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP1100</t>
+          <t>2026_OB_STG_BSMP1100</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -5009,7 +5009,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP1100</t>
+          <t>2026_OB_STG_BSMP1100</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -5036,7 +5036,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP1100</t>
+          <t>2026_OB_STG_BSMP1100</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -5063,7 +5063,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP1300</t>
+          <t>2026_OB_STG_BSMP1300</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -5090,7 +5090,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP1300</t>
+          <t>2026_OB_STG_BSMP1300</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -5117,7 +5117,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP1300</t>
+          <t>2026_OB_STG_BSMP1300</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -5144,7 +5144,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP1300</t>
+          <t>2026_OB_STG_BSMP1300</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -5171,7 +5171,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP1300</t>
+          <t>2026_OB_STG_BSMP1300</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -5198,7 +5198,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP1300</t>
+          <t>2026_OB_STG_BSMP1300</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -5225,7 +5225,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP1300</t>
+          <t>2026_OB_STG_BSMP1300</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -5252,7 +5252,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP0300</t>
+          <t>2026_OB_STG_BSMP0300</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -5279,7 +5279,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP0300</t>
+          <t>2026_OB_STG_BSMP0300</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -5306,7 +5306,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP0300</t>
+          <t>2026_OB_STG_BSMP0300</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -5333,7 +5333,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP0300</t>
+          <t>2026_OB_STG_BSMP0300</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -5360,7 +5360,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP0300</t>
+          <t>2026_OB_STG_BSMP0300</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -5387,7 +5387,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP0300</t>
+          <t>2026_OB_STG_BSMP0300</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -5414,7 +5414,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP0300</t>
+          <t>2026_OB_STG_BSMP0300</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -5441,7 +5441,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP0300</t>
+          <t>2026_OB_STG_BSMP0300</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -5468,7 +5468,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP3020</t>
+          <t>2026_OB_STG_BSMP3020</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -5495,7 +5495,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP3020</t>
+          <t>2026_OB_STG_BSMP3020</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -5522,7 +5522,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP3020</t>
+          <t>2026_OB_STG_BSMP3020</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -5549,7 +5549,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP3020</t>
+          <t>2026_OB_STG_BSMP3020</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -5576,7 +5576,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP3020</t>
+          <t>2026_OB_STG_BSMP3020</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -5603,7 +5603,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP3020</t>
+          <t>2026_OB_STG_BSMP3020</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -5630,7 +5630,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP3020</t>
+          <t>2026_OB_STG_BSMP3020</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -5657,7 +5657,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP3020</t>
+          <t>2026_OB_STG_BSMP3020</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -5684,7 +5684,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP3020</t>
+          <t>2026_OB_STG_BSMP3020</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -5711,7 +5711,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA2500</t>
+          <t>2026_OB_STG_BSEA2500</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -5738,7 +5738,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA2500</t>
+          <t>2026_OB_STG_BSEA2500</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -5765,7 +5765,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA2500</t>
+          <t>2026_OB_STG_BSEA2500</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -5792,7 +5792,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA2500</t>
+          <t>2026_OB_STG_BSEA2500</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -5819,7 +5819,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA2500</t>
+          <t>2026_OB_STG_BSEA2500</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -5846,7 +5846,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA2500</t>
+          <t>2026_OB_STG_BSEA2500</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -5873,7 +5873,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP2610</t>
+          <t>2026_OB_STG_BSMP2610</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -5900,7 +5900,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP2610</t>
+          <t>2026_OB_STG_BSMP2610</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -5927,7 +5927,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP2610</t>
+          <t>2026_OB_STG_BSMP2610</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -5954,7 +5954,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP2610</t>
+          <t>2026_OB_STG_BSMP2610</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -5981,7 +5981,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP2610</t>
+          <t>2026_OB_STG_BSMP2610</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -6008,7 +6008,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP2610</t>
+          <t>2026_OB_STG_BSMP2610</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -6035,7 +6035,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA2600</t>
+          <t>2026_OB_STG_BSEA2600</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -6062,7 +6062,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA2600</t>
+          <t>2026_OB_STG_BSEA2600</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -6089,7 +6089,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA2600</t>
+          <t>2026_OB_STG_BSEA2600</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -6116,7 +6116,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA2600</t>
+          <t>2026_OB_STG_BSEA2600</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -6143,7 +6143,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA2600</t>
+          <t>2026_OB_STG_BSEA2600</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -6170,7 +6170,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA2600</t>
+          <t>2026_OB_STG_BSEA2600</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -6197,7 +6197,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA2600</t>
+          <t>2026_OB_STG_BSEA2600</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -6224,7 +6224,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>OB_STG_BSTA4100</t>
+          <t>2026_OB_STG_BSTA4100</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -6251,7 +6251,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>OB_STG_BSTA4100</t>
+          <t>2026_OB_STG_BSTA4100</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -6278,7 +6278,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>OB_STG_BSTA4100</t>
+          <t>2026_OB_STG_BSTA4100</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -6305,7 +6305,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>OB_STG_BSTA4100</t>
+          <t>2026_OB_STG_BSTA4100</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -6332,7 +6332,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>OB_STG_BSTA4100</t>
+          <t>2026_OB_STG_BSTA4100</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -6359,7 +6359,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>OB_STG_BSTA4100</t>
+          <t>2026_OB_STG_BSTA4100</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -6386,7 +6386,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP1810</t>
+          <t>2026_OB_STG_BSCP1810</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -6413,7 +6413,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP1810</t>
+          <t>2026_OB_STG_BSCP1810</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -6440,7 +6440,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP1810</t>
+          <t>2026_OB_STG_BSCP1810</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -6467,7 +6467,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP1810</t>
+          <t>2026_OB_STG_BSCP1810</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -6494,7 +6494,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP1810</t>
+          <t>2026_OB_STG_BSCP1810</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -6521,7 +6521,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP1810</t>
+          <t>2026_OB_STG_BSCP1810</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -6548,7 +6548,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS0510</t>
+          <t>2026_OB_STG_BSCS0510</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -6575,7 +6575,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS0510</t>
+          <t>2026_OB_STG_BSCS0510</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -6602,7 +6602,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS0510</t>
+          <t>2026_OB_STG_BSCS0510</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -6629,7 +6629,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS0510</t>
+          <t>2026_OB_STG_BSCS0510</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -6656,7 +6656,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS0510</t>
+          <t>2026_OB_STG_BSCS0510</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -6683,7 +6683,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>OB_STG_BSOP3310</t>
+          <t>2026_OB_STG_BSOP3310</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -6710,7 +6710,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>OB_STG_BSOP3310</t>
+          <t>2026_OB_STG_BSOP3310</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -6737,7 +6737,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>OB_STG_BSOP3310</t>
+          <t>2026_OB_STG_BSOP3310</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -6764,7 +6764,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>OB_STG_BSOP3310</t>
+          <t>2026_OB_STG_BSOP3310</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -6791,7 +6791,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>OB_STG_BSOP3310</t>
+          <t>2026_OB_STG_BSOP3310</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -6818,7 +6818,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>OB_STG_BSOP3310</t>
+          <t>2026_OB_STG_BSOP3310</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -6845,7 +6845,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP2400</t>
+          <t>2026_OB_STG_BSCP2400</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -6872,7 +6872,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP2400</t>
+          <t>2026_OB_STG_BSCP2400</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -6899,7 +6899,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP2400</t>
+          <t>2026_OB_STG_BSCP2400</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -6926,7 +6926,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP2400</t>
+          <t>2026_OB_STG_BSCP2400</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -6953,7 +6953,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP2400</t>
+          <t>2026_OB_STG_BSCP2400</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -6980,7 +6980,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP2400</t>
+          <t>2026_OB_STG_BSCP2400</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -7007,7 +7007,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP2400</t>
+          <t>2026_OB_STG_BSCP2400</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -7034,7 +7034,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP2400</t>
+          <t>2026_OB_STG_BSCP2400</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -7061,7 +7061,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP2400</t>
+          <t>2026_OB_STG_BSCP2400</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -7088,7 +7088,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP0208</t>
+          <t>2026_OB_STG_BSCP0208</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -7115,7 +7115,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP0208</t>
+          <t>2026_OB_STG_BSCP0208</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -7142,7 +7142,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP0208</t>
+          <t>2026_OB_STG_BSCP0208</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -7169,7 +7169,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP0208</t>
+          <t>2026_OB_STG_BSCP0208</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -7196,7 +7196,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP0208</t>
+          <t>2026_OB_STG_BSCP0208</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -7223,7 +7223,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP0208</t>
+          <t>2026_OB_STG_BSCP0208</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -7250,7 +7250,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP0208</t>
+          <t>2026_OB_STG_BSCP0208</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -7277,7 +7277,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP0208</t>
+          <t>2026_OB_STG_BSCP0208</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -7304,7 +7304,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP0208</t>
+          <t>2026_OB_STG_BSCP0208</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -7331,7 +7331,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP3500</t>
+          <t>2026_OB_STG_BSCP3500</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -7358,7 +7358,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP3500</t>
+          <t>2026_OB_STG_BSCP3500</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -7385,7 +7385,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP3500</t>
+          <t>2026_OB_STG_BSCP3500</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -7412,7 +7412,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP3500</t>
+          <t>2026_OB_STG_BSCP3500</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -7439,7 +7439,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP3500</t>
+          <t>2026_OB_STG_BSCP3500</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -7466,7 +7466,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP3500</t>
+          <t>2026_OB_STG_BSCP3500</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -7493,7 +7493,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP3500</t>
+          <t>2026_OB_STG_BSCP3500</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -7520,7 +7520,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP1800</t>
+          <t>2026_OB_STG_BSCP1800</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -7547,7 +7547,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP1800</t>
+          <t>2026_OB_STG_BSCP1800</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -7574,7 +7574,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP1800</t>
+          <t>2026_OB_STG_BSCP1800</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -7601,7 +7601,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP1800</t>
+          <t>2026_OB_STG_BSCP1800</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -7628,7 +7628,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP1800</t>
+          <t>2026_OB_STG_BSCP1800</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -7655,7 +7655,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP1800</t>
+          <t>2026_OB_STG_BSCP1800</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -7682,7 +7682,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP1800</t>
+          <t>2026_OB_STG_BSCP1800</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -7709,7 +7709,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>OB_STG_BSTA5000</t>
+          <t>2026_OB_STG_BSTA5000</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -7736,7 +7736,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>OB_STG_BSTA5000</t>
+          <t>2026_OB_STG_BSTA5000</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -7763,7 +7763,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>OB_STG_BSTA5000</t>
+          <t>2026_OB_STG_BSTA5000</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -7790,7 +7790,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>OB_STG_BSOP3100</t>
+          <t>2026_OB_STG_BSOP3100</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -7817,7 +7817,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>OB_STG_BSOP3100</t>
+          <t>2026_OB_STG_BSOP3100</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -7844,7 +7844,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>OB_STG_BSOP3100</t>
+          <t>2026_OB_STG_BSOP3100</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -7871,7 +7871,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>OB_STG_BSOP3100</t>
+          <t>2026_OB_STG_BSOP3100</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -7898,7 +7898,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>OB_STG_BSOP3100</t>
+          <t>2026_OB_STG_BSOP3100</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -7925,7 +7925,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>OB_STG_BSOP3100</t>
+          <t>2026_OB_STG_BSOP3100</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -7952,7 +7952,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>OB_STG_BSOP3600</t>
+          <t>2026_OB_STG_BSOP3600</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -7979,7 +7979,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>OB_STG_BSOP3600</t>
+          <t>2026_OB_STG_BSOP3600</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -8006,7 +8006,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>OB_STG_BSOP3600</t>
+          <t>2026_OB_STG_BSOP3600</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -8033,7 +8033,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>OB_STG_BSOP3600</t>
+          <t>2026_OB_STG_BSOP3600</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -8060,7 +8060,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>OB_STG_BSOP3600</t>
+          <t>2026_OB_STG_BSOP3600</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -8087,7 +8087,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>OB_STG_BSOP3600</t>
+          <t>2026_OB_STG_BSOP3600</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -8114,7 +8114,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>OB_STG_BSU9095</t>
+          <t>2026_OB_STG_BSU9095</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -8141,7 +8141,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>OB_STG_BSU9095</t>
+          <t>2026_OB_STG_BSU9095</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -8168,7 +8168,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>OB_STG_BSU9095</t>
+          <t>2026_OB_STG_BSU9095</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -8195,7 +8195,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>OB_STG_BSU9095</t>
+          <t>2026_OB_STG_BSU9095</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -8222,7 +8222,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA2202</t>
+          <t>2026_OB_STG_BSEA2202</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -8249,7 +8249,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA2202</t>
+          <t>2026_OB_STG_BSEA2202</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -8276,7 +8276,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA2202</t>
+          <t>2026_OB_STG_BSEA2202</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -8303,7 +8303,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA2202</t>
+          <t>2026_OB_STG_BSEA2202</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -8330,7 +8330,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA2202</t>
+          <t>2026_OB_STG_BSEA2202</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -8357,7 +8357,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA2202</t>
+          <t>2026_OB_STG_BSEA2202</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -8384,7 +8384,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA2202</t>
+          <t>2026_OB_STG_BSEA2202</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -8411,7 +8411,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>OB_STG_BSTA4110</t>
+          <t>2026_OB_STG_BSTA4110</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -8438,7 +8438,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>OB_STG_BSTA4110</t>
+          <t>2026_OB_STG_BSTA4110</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -8465,7 +8465,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>OB_STG_BSTA4110</t>
+          <t>2026_OB_STG_BSTA4110</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -8492,7 +8492,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>OB_STG_BSTA4110</t>
+          <t>2026_OB_STG_BSTA4110</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -8519,7 +8519,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>OB_STG_BSTA4330</t>
+          <t>2026_OB_STG_BSTA4330</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -8546,7 +8546,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>OB_STG_BSTA4330</t>
+          <t>2026_OB_STG_BSTA4330</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -8573,7 +8573,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>OB_STG_BSTA4330</t>
+          <t>2026_OB_STG_BSTA4330</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -8600,7 +8600,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>OB_STG_BSTA4330</t>
+          <t>2026_OB_STG_BSTA4330</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -8627,7 +8627,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>OB_STG_BSTA4330</t>
+          <t>2026_OB_STG_BSTA4330</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -8654,7 +8654,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>OB_STG_BSTA4330</t>
+          <t>2026_OB_STG_BSTA4330</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -8681,7 +8681,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP1310</t>
+          <t>2026_OB_STG_BSMP1310</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -8708,7 +8708,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP1310</t>
+          <t>2026_OB_STG_BSMP1310</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -8735,7 +8735,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP1310</t>
+          <t>2026_OB_STG_BSMP1310</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -8762,7 +8762,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP1310</t>
+          <t>2026_OB_STG_BSMP1310</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -8789,7 +8789,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP1310</t>
+          <t>2026_OB_STG_BSMP1310</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -8816,7 +8816,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP1310</t>
+          <t>2026_OB_STG_BSMP1310</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -8843,7 +8843,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA2210</t>
+          <t>2026_OB_STG_BSEA2210</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -8870,7 +8870,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA2210</t>
+          <t>2026_OB_STG_BSEA2210</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -8897,7 +8897,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA2210</t>
+          <t>2026_OB_STG_BSEA2210</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -8924,7 +8924,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA2210</t>
+          <t>2026_OB_STG_BSEA2210</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -8951,7 +8951,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA2210</t>
+          <t>2026_OB_STG_BSEA2210</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -8978,7 +8978,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA2210</t>
+          <t>2026_OB_STG_BSEA2210</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -9005,7 +9005,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA2210</t>
+          <t>2026_OB_STG_BSEA2210</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -9032,7 +9032,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>OB_STG_BSTA4010</t>
+          <t>2026_OB_STG_BSTA4010</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -9059,7 +9059,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>OB_STG_BSTA4010</t>
+          <t>2026_OB_STG_BSTA4010</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -9086,7 +9086,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>OB_STG_BSTA4010</t>
+          <t>2026_OB_STG_BSTA4010</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -9113,7 +9113,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>OB_STG_BSTA4010</t>
+          <t>2026_OB_STG_BSTA4010</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -9140,7 +9140,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>OB_STG_BSTA4010</t>
+          <t>2026_OB_STG_BSTA4010</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -9167,7 +9167,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>OB_STG_BSOP3800</t>
+          <t>2026_OB_STG_BSOP3800</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -9194,7 +9194,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>OB_STG_BSOP3800</t>
+          <t>2026_OB_STG_BSOP3800</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -9221,7 +9221,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>OB_STG_BSOP3800</t>
+          <t>2026_OB_STG_BSOP3800</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -9248,7 +9248,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>OB_STG_BSOP3800</t>
+          <t>2026_OB_STG_BSOP3800</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -9275,7 +9275,7 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>OB_STG_BSOP3800</t>
+          <t>2026_OB_STG_BSOP3800</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -9302,7 +9302,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>OB_STG_BAA9911</t>
+          <t>2026_OB_STG_BAA9911</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -9329,7 +9329,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>OB_STG_BSTR2213</t>
+          <t>2026_OB_STG_BSTR2213</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -9356,7 +9356,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>OB_STG_BSTR2213</t>
+          <t>2026_OB_STG_BSTR2213</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -9383,7 +9383,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>OB_STG_BSTR2213</t>
+          <t>2026_OB_STG_BSTR2213</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -9410,7 +9410,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>OB_STG_BSTR2213</t>
+          <t>2026_OB_STG_BSTR2213</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -9437,7 +9437,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>OB_STG_BSTR2213</t>
+          <t>2026_OB_STG_BSTR2213</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -9464,7 +9464,7 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>OB_STG_BSTR2213</t>
+          <t>2026_OB_STG_BSTR2213</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -9491,7 +9491,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>OB_STG_BSTR2213</t>
+          <t>2026_OB_STG_BSTR2213</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -9518,7 +9518,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA2280</t>
+          <t>2026_OB_STG_BSEA2280</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -9545,7 +9545,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA2280</t>
+          <t>2026_OB_STG_BSEA2280</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -9572,7 +9572,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA2280</t>
+          <t>2026_OB_STG_BSEA2280</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -9599,7 +9599,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA2280</t>
+          <t>2026_OB_STG_BSEA2280</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -9626,7 +9626,7 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA2280</t>
+          <t>2026_OB_STG_BSEA2280</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -9653,7 +9653,7 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA2280</t>
+          <t>2026_OB_STG_BSEA2280</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -9680,7 +9680,7 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA2280</t>
+          <t>2026_OB_STG_BSEA2280</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -9707,7 +9707,7 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA2810</t>
+          <t>2026_OB_STG_BSEA2810</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -9734,7 +9734,7 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA2810</t>
+          <t>2026_OB_STG_BSEA2810</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -9761,7 +9761,7 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA2810</t>
+          <t>2026_OB_STG_BSEA2810</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -9788,7 +9788,7 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA2810</t>
+          <t>2026_OB_STG_BSEA2810</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -9815,7 +9815,7 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA2810</t>
+          <t>2026_OB_STG_BSEA2810</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -9842,7 +9842,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA2810</t>
+          <t>2026_OB_STG_BSEA2810</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -9869,7 +9869,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS1010</t>
+          <t>2026_OB_STG_BSCS1010</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -9896,7 +9896,7 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS1010</t>
+          <t>2026_OB_STG_BSCS1010</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -9923,7 +9923,7 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS1010</t>
+          <t>2026_OB_STG_BSCS1010</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -9950,7 +9950,7 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS1010</t>
+          <t>2026_OB_STG_BSCS1010</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -9977,7 +9977,7 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS1010</t>
+          <t>2026_OB_STG_BSCS1010</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -10004,7 +10004,7 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS1010</t>
+          <t>2026_OB_STG_BSCS1010</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -10031,7 +10031,7 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS1010</t>
+          <t>2026_OB_STG_BSCS1010</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -10058,7 +10058,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP1500</t>
+          <t>2026_OB_STG_BSCP1500</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -10085,7 +10085,7 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP1500</t>
+          <t>2026_OB_STG_BSCP1500</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -10112,7 +10112,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP1500</t>
+          <t>2026_OB_STG_BSCP1500</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -10139,7 +10139,7 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP1500</t>
+          <t>2026_OB_STG_BSCP1500</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -10166,7 +10166,7 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP1500</t>
+          <t>2026_OB_STG_BSCP1500</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -10193,7 +10193,7 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP1500</t>
+          <t>2026_OB_STG_BSCP1500</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -10220,7 +10220,7 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP1500</t>
+          <t>2026_OB_STG_BSCP1500</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -10247,7 +10247,7 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP1500</t>
+          <t>2026_OB_STG_BSCP1500</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -10274,7 +10274,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP1407</t>
+          <t>2026_OB_STG_BSCP1407</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -10301,7 +10301,7 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP1407</t>
+          <t>2026_OB_STG_BSCP1407</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -10328,7 +10328,7 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP1407</t>
+          <t>2026_OB_STG_BSCP1407</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -10355,7 +10355,7 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP1407</t>
+          <t>2026_OB_STG_BSCP1407</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -10382,7 +10382,7 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP1407</t>
+          <t>2026_OB_STG_BSCP1407</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -10409,7 +10409,7 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP1407</t>
+          <t>2026_OB_STG_BSCP1407</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -10436,7 +10436,7 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP1407</t>
+          <t>2026_OB_STG_BSCP1407</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -10463,7 +10463,7 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>OB_STG_BSU9208</t>
+          <t>2026_OB_STG_BSU9208</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -10490,7 +10490,7 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>OB_STG_BSU9208</t>
+          <t>2026_OB_STG_BSU9208</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -10517,7 +10517,7 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>OB_STG_BSU9208</t>
+          <t>2026_OB_STG_BSU9208</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -10544,7 +10544,7 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>OB_STG_BSU9208</t>
+          <t>2026_OB_STG_BSU9208</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -10571,7 +10571,7 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS1405</t>
+          <t>2026_OB_STG_BSCS1405</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -10598,7 +10598,7 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS1405</t>
+          <t>2026_OB_STG_BSCS1405</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -10625,7 +10625,7 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS1405</t>
+          <t>2026_OB_STG_BSCS1405</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -10652,7 +10652,7 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS1405</t>
+          <t>2026_OB_STG_BSCS1405</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -10679,7 +10679,7 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS1405</t>
+          <t>2026_OB_STG_BSCS1405</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -10706,7 +10706,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS1405</t>
+          <t>2026_OB_STG_BSCS1405</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -10733,7 +10733,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS1403</t>
+          <t>2026_OB_STG_BSCS1403</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -10760,7 +10760,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS1403</t>
+          <t>2026_OB_STG_BSCS1403</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -10787,7 +10787,7 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS1403</t>
+          <t>2026_OB_STG_BSCS1403</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -10814,7 +10814,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS1403</t>
+          <t>2026_OB_STG_BSCS1403</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -10841,7 +10841,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS1403</t>
+          <t>2026_OB_STG_BSCS1403</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -10868,7 +10868,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS1403</t>
+          <t>2026_OB_STG_BSCS1403</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -10895,7 +10895,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS1403</t>
+          <t>2026_OB_STG_BSCS1403</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -10922,7 +10922,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA14081</t>
+          <t>2026_OB_STG_BSEA14081</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -10949,7 +10949,7 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA14081</t>
+          <t>2026_OB_STG_BSEA14081</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -10976,7 +10976,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA14081</t>
+          <t>2026_OB_STG_BSEA14081</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -11003,7 +11003,7 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA14081</t>
+          <t>2026_OB_STG_BSEA14081</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -11030,7 +11030,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP3000</t>
+          <t>2026_OB_STG_BSMP3000</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -11057,7 +11057,7 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP3000</t>
+          <t>2026_OB_STG_BSMP3000</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -11084,7 +11084,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP3000</t>
+          <t>2026_OB_STG_BSMP3000</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -11111,7 +11111,7 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP3000</t>
+          <t>2026_OB_STG_BSMP3000</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -11138,7 +11138,7 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP3000</t>
+          <t>2026_OB_STG_BSMP3000</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -11165,7 +11165,7 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP3000</t>
+          <t>2026_OB_STG_BSMP3000</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -11192,7 +11192,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP3000</t>
+          <t>2026_OB_STG_BSMP3000</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -11219,7 +11219,7 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP3700</t>
+          <t>2026_OB_STG_BSMP3700</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
@@ -11246,7 +11246,7 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP3700</t>
+          <t>2026_OB_STG_BSMP3700</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -11273,7 +11273,7 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP3700</t>
+          <t>2026_OB_STG_BSMP3700</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -11300,7 +11300,7 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP3700</t>
+          <t>2026_OB_STG_BSMP3700</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -11327,7 +11327,7 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP3700</t>
+          <t>2026_OB_STG_BSMP3700</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -11354,7 +11354,7 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP3700</t>
+          <t>2026_OB_STG_BSMP3700</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -11381,7 +11381,7 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP3700</t>
+          <t>2026_OB_STG_BSMP3700</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -11408,7 +11408,7 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP1401</t>
+          <t>2026_OB_STG_BSMP1401</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -11435,7 +11435,7 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP1401</t>
+          <t>2026_OB_STG_BSMP1401</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -11462,7 +11462,7 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP1401</t>
+          <t>2026_OB_STG_BSMP1401</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -11489,7 +11489,7 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP1401</t>
+          <t>2026_OB_STG_BSMP1401</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -11516,7 +11516,7 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP1401</t>
+          <t>2026_OB_STG_BSMP1401</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -11543,7 +11543,7 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>OB_STG_BSTA1003</t>
+          <t>2026_OB_STG_BSTA1003</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -11570,7 +11570,7 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>OB_STG_BSTA1003</t>
+          <t>2026_OB_STG_BSTA1003</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -11597,7 +11597,7 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>OB_STG_BSTA1003</t>
+          <t>2026_OB_STG_BSTA1003</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -11624,7 +11624,7 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>OB_STG_BSTA1003</t>
+          <t>2026_OB_STG_BSTA1003</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -11651,7 +11651,7 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>OB_STG_BSTA1002</t>
+          <t>2026_OB_STG_BSTA1002</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
@@ -11678,7 +11678,7 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>OB_STG_BSTA1002</t>
+          <t>2026_OB_STG_BSTA1002</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
@@ -11705,7 +11705,7 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>OB_STG_BSTA1002</t>
+          <t>2026_OB_STG_BSTA1002</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
@@ -11732,7 +11732,7 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>OB_STG_BSTA1002</t>
+          <t>2026_OB_STG_BSTA1002</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
@@ -11759,7 +11759,7 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>OB_STG_BSTA1002</t>
+          <t>2026_OB_STG_BSTA1002</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
@@ -11786,7 +11786,7 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP1404</t>
+          <t>2026_OB_STG_BSCP1404</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
@@ -11813,7 +11813,7 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP1404</t>
+          <t>2026_OB_STG_BSCP1404</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
@@ -11840,7 +11840,7 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP1404</t>
+          <t>2026_OB_STG_BSCP1404</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
@@ -11867,7 +11867,7 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP1404</t>
+          <t>2026_OB_STG_BSCP1404</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
@@ -11894,7 +11894,7 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP1404</t>
+          <t>2026_OB_STG_BSCP1404</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
@@ -11921,7 +11921,7 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>OB_STG_BSOP1901</t>
+          <t>2026_OB_STG_BSOP1901</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
@@ -11948,7 +11948,7 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>OB_STG_BSOP1901</t>
+          <t>2026_OB_STG_BSOP1901</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
@@ -11975,7 +11975,7 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>OB_STG_BSOP1901</t>
+          <t>2026_OB_STG_BSOP1901</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
@@ -12002,7 +12002,7 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>OB_STG_BSOP1901</t>
+          <t>2026_OB_STG_BSOP1901</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -12029,7 +12029,7 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>OB_STG_BSOP1901</t>
+          <t>2026_OB_STG_BSOP1901</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
@@ -12056,7 +12056,7 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>OB_STG_BSU1405</t>
+          <t>2026_OB_STG_BSU1405</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
@@ -12083,7 +12083,7 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>OB_STG_BSU1405</t>
+          <t>2026_OB_STG_BSU1405</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
@@ -12110,7 +12110,7 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>OB_STG_BSU1405</t>
+          <t>2026_OB_STG_BSU1405</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
@@ -12137,7 +12137,7 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>OB_STG_BSOP2214</t>
+          <t>2026_OB_STG_BSOP2214</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
@@ -12164,7 +12164,7 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>OB_STG_BSOP2214</t>
+          <t>2026_OB_STG_BSOP2214</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
@@ -12191,7 +12191,7 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>OB_STG_BSOP2214</t>
+          <t>2026_OB_STG_BSOP2214</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
@@ -12218,7 +12218,7 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>OB_STG_BSOP2214</t>
+          <t>2026_OB_STG_BSOP2214</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
@@ -12245,7 +12245,7 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>OB_STG_BSOP2214</t>
+          <t>2026_OB_STG_BSOP2214</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
@@ -12272,7 +12272,7 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS1404</t>
+          <t>2026_OB_STG_BSCS1404</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
@@ -12299,7 +12299,7 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS1404</t>
+          <t>2026_OB_STG_BSCS1404</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
@@ -12326,7 +12326,7 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS1404</t>
+          <t>2026_OB_STG_BSCS1404</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
@@ -12353,7 +12353,7 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS1404</t>
+          <t>2026_OB_STG_BSCS1404</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
@@ -12380,7 +12380,7 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS1404</t>
+          <t>2026_OB_STG_BSCS1404</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
@@ -12407,7 +12407,7 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS1404</t>
+          <t>2026_OB_STG_BSCS1404</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
@@ -12434,7 +12434,7 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS1404</t>
+          <t>2026_OB_STG_BSCS1404</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
@@ -12461,7 +12461,7 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS1404</t>
+          <t>2026_OB_STG_BSCS1404</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
